--- a/data/Bekleyen_Siparisler.xlsx
+++ b/data/Bekleyen_Siparisler.xlsx
@@ -482,22 +482,22 @@
       </c>
       <c s="3" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">5901522</t>
+          <t xml:space="preserve">5333668</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D4">
         <is>
-          <t xml:space="preserve">GÖKKUŞAĞI KINA EVİ SABAH DOKSÖZ</t>
+          <t xml:space="preserve">GÜL GIDA ABDULRAKİP HERGÜL VE ORTAKLARI.</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">37100</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">METİN ANASIZ</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G4">
@@ -512,7 +512,7 @@
       </c>
       <c s="3" t="inlineStr" r="I4">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">125474</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="J4">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c s="4" r="L4">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c s="4" r="M4">
         <v>0</v>
@@ -535,31 +535,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O4">
-        <v>2161.56</v>
+        <v>3859.92</v>
       </c>
       <c s="4" r="P4">
-        <v>79027.20</v>
+        <v>141120</v>
       </c>
       <c s="4" r="Q4">
-        <v>21598.13</v>
+        <v>0</v>
       </c>
       <c s="4" r="R4">
-        <v>0</v>
+        <v>35661.02</v>
       </c>
       <c s="4" r="S4">
         <v>0</v>
       </c>
       <c s="4" r="T4">
-        <v>21598.13</v>
+        <v>35661.02</v>
       </c>
       <c s="4" r="U4">
-        <v>57429.07</v>
+        <v>105458.98</v>
       </c>
       <c s="4" r="V4">
-        <v>5742.91</v>
+        <v>10545.90</v>
       </c>
       <c s="4" r="W4">
-        <v>63171.97</v>
+        <v>116004.87</v>
       </c>
       <c s="5" t="str" r="X4"/>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c s="3" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">5333668</t>
+          <t xml:space="preserve">5050991</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D5">
         <is>
-          <t xml:space="preserve">GÜL GIDA ABDULRAKİP HERGÜL VE ORTAKLARI.</t>
+          <t xml:space="preserve">GÜRKAN HALI SAHA VE MARKET-BONA GÜRKAN</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E5">
@@ -596,17 +596,17 @@
       </c>
       <c s="3" t="inlineStr" r="G5">
         <is>
-          <t xml:space="preserve">11743</t>
+          <t xml:space="preserve">11543</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">PET PC KOLA 1.5L 12X 70KCAL</t>
+          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I5">
         <is>
-          <t xml:space="preserve">125474</t>
+          <t xml:space="preserve">499691, 124957</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="J5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c s="4" r="L5">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c s="4" r="M5">
         <v>0</v>
@@ -629,31 +629,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O5">
-        <v>3859.92</v>
+        <v>1579.98</v>
       </c>
       <c s="4" r="P5">
-        <v>141120</v>
+        <v>41400</v>
       </c>
       <c s="4" r="Q5">
         <v>0</v>
       </c>
       <c s="4" r="R5">
-        <v>35661.02</v>
+        <v>9306.72</v>
       </c>
       <c s="4" r="S5">
         <v>0</v>
       </c>
       <c s="4" r="T5">
-        <v>35661.02</v>
+        <v>9306.72</v>
       </c>
       <c s="4" r="U5">
-        <v>105458.98</v>
+        <v>32093.28</v>
       </c>
       <c s="4" r="V5">
-        <v>10545.90</v>
+        <v>3209.33</v>
       </c>
       <c s="4" r="W5">
-        <v>116004.87</v>
+        <v>35302.61</v>
       </c>
       <c s="5" t="str" r="X5"/>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c s="3" t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">11543</t>
+          <t xml:space="preserve">11743</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
+          <t xml:space="preserve">PET PC KOLA 1.5L 12X 70KCAL</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I6">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c s="4" r="L6">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c s="4" r="M6">
         <v>0</v>
@@ -723,31 +723,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O6">
-        <v>1579.98</v>
+        <v>193.00</v>
       </c>
       <c s="4" r="P6">
-        <v>41400</v>
+        <v>7056</v>
       </c>
       <c s="4" r="Q6">
         <v>0</v>
       </c>
       <c s="4" r="R6">
-        <v>9306.72</v>
+        <v>1255.97</v>
       </c>
       <c s="4" r="S6">
         <v>0</v>
       </c>
       <c s="4" r="T6">
-        <v>9306.72</v>
+        <v>1255.97</v>
       </c>
       <c s="4" r="U6">
-        <v>32093.28</v>
+        <v>5800.03</v>
       </c>
       <c s="4" r="V6">
-        <v>3209.33</v>
+        <v>580.00</v>
       </c>
       <c s="4" r="W6">
-        <v>35302.61</v>
+        <v>6380.04</v>
       </c>
       <c s="5" t="str" r="X6"/>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c s="3" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">5050991</t>
+          <t xml:space="preserve">5307975</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D7">
         <is>
-          <t xml:space="preserve">GÜRKAN HALI SAHA VE MARKET-BONA GÜRKAN</t>
+          <t xml:space="preserve">ME-KA GIDA TİC. TOPTAN MEHMET KAÇAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E7">
@@ -784,17 +784,17 @@
       </c>
       <c s="3" t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">11743</t>
+          <t xml:space="preserve">11813</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">PET PC KOLA 1.5L 12X 70KCAL</t>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I7">
         <is>
-          <t xml:space="preserve">499691, 124957</t>
+          <t xml:space="preserve">126105</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="J7">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c s="4" r="L7">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c s="4" r="M7">
         <v>0</v>
@@ -817,31 +817,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O7">
-        <v>193.00</v>
+        <v>4620</v>
       </c>
       <c s="4" r="P7">
-        <v>7056</v>
+        <v>229782</v>
       </c>
       <c s="4" r="Q7">
         <v>0</v>
       </c>
       <c s="4" r="R7">
-        <v>1255.97</v>
+        <v>77045.90</v>
       </c>
       <c s="4" r="S7">
         <v>0</v>
       </c>
       <c s="4" r="T7">
-        <v>1255.97</v>
+        <v>77045.90</v>
       </c>
       <c s="4" r="U7">
-        <v>5800.03</v>
+        <v>152736.10</v>
       </c>
       <c s="4" r="V7">
-        <v>580.00</v>
+        <v>15273.61</v>
       </c>
       <c s="4" r="W7">
-        <v>6380.04</v>
+        <v>168009.70</v>
       </c>
       <c s="5" t="str" r="X7"/>
     </row>
@@ -858,37 +858,37 @@
       </c>
       <c s="3" t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">6144426</t>
+          <t xml:space="preserve">5210711</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D8">
         <is>
-          <t xml:space="preserve">MEHMET AŞKAROĞLU</t>
+          <t xml:space="preserve">SEMIOGULLARI GIDA</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">37356</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">SERAY AKSOY</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G8">
         <is>
-          <t xml:space="preserve">11743</t>
+          <t xml:space="preserve">11813</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">PET PC KOLA 1.5L 12X 70KCAL</t>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I8">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">228718</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="J8">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c s="4" r="L8">
-        <v>3</v>
+        <v>350</v>
       </c>
       <c s="4" r="M8">
         <v>0</v>
@@ -911,31 +911,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O8">
-        <v>57.90</v>
+        <v>4620</v>
       </c>
       <c s="4" r="P8">
-        <v>2116.80</v>
+        <v>229782</v>
       </c>
       <c s="4" r="Q8">
         <v>0</v>
       </c>
       <c s="4" r="R8">
-        <v>223.32</v>
+        <v>77045.90</v>
       </c>
       <c s="4" r="S8">
         <v>0</v>
       </c>
       <c s="4" r="T8">
-        <v>223.32</v>
+        <v>77045.90</v>
       </c>
       <c s="4" r="U8">
-        <v>1893.48</v>
+        <v>152736.10</v>
       </c>
       <c s="4" r="V8">
-        <v>189.35</v>
+        <v>15273.61</v>
       </c>
       <c s="4" r="W8">
-        <v>2082.83</v>
+        <v>168009.70</v>
       </c>
       <c s="5" t="str" r="X8"/>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c s="3" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">6144426</t>
+          <t xml:space="preserve">6142940</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D9">
         <is>
-          <t xml:space="preserve">MEHMET AŞKAROĞLU</t>
+          <t xml:space="preserve">SİBELA SÜPERMAKET AŞAĞIOKÇULAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">37356</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">SERAY AKSOY</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G9">
         <is>
-          <t xml:space="preserve">11813</t>
+          <t xml:space="preserve">11845</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
+          <t xml:space="preserve">CAN STNG KIR MEY 500ML 12X</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c s="4" r="L9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c s="4" r="M9">
         <v>0</v>
@@ -1005,31 +1005,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O9">
-        <v>132</v>
+        <v>8.43</v>
       </c>
       <c s="4" r="P9">
-        <v>6565.20</v>
+        <v>1083.12</v>
       </c>
       <c s="4" r="Q9">
         <v>0</v>
       </c>
       <c s="4" r="R9">
-        <v>1449.30</v>
+        <v>400.75</v>
       </c>
       <c s="4" r="S9">
         <v>0</v>
       </c>
       <c s="4" r="T9">
-        <v>1449.30</v>
+        <v>400.75</v>
       </c>
       <c s="4" r="U9">
-        <v>5115.90</v>
+        <v>682.37</v>
       </c>
       <c s="4" r="V9">
-        <v>511.59</v>
+        <v>68.24</v>
       </c>
       <c s="4" r="W9">
-        <v>5627.49</v>
+        <v>750.60</v>
       </c>
       <c s="5" t="str" r="X9"/>
     </row>
@@ -1046,32 +1046,32 @@
       </c>
       <c s="3" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">6144426</t>
+          <t xml:space="preserve">6142940</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D10">
         <is>
-          <t xml:space="preserve">MEHMET AŞKAROĞLU</t>
+          <t xml:space="preserve">SİBELA SÜPERMAKET AŞAĞIOKÇULAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">37356</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">SERAY AKSOY</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">11452</t>
+          <t xml:space="preserve">11543</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">PET PC KOLA 2.5L 6X 100KCAL DRS</t>
+          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I10">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c s="4" r="L10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c s="4" r="M10">
         <v>0</v>
@@ -1099,31 +1099,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O10">
-        <v>192.00</v>
+        <v>505.59</v>
       </c>
       <c s="4" r="P10">
-        <v>5867.28</v>
+        <v>12024.96</v>
       </c>
       <c s="4" r="Q10">
-        <v>0</v>
+        <v>176.02</v>
       </c>
       <c s="4" r="R10">
-        <v>1521.68</v>
+        <v>3223.89</v>
       </c>
       <c s="4" r="S10">
         <v>0</v>
       </c>
       <c s="4" r="T10">
-        <v>1521.68</v>
+        <v>3399.91</v>
       </c>
       <c s="4" r="U10">
-        <v>4345.60</v>
+        <v>8625.05</v>
       </c>
       <c s="4" r="V10">
-        <v>434.56</v>
+        <v>862.50</v>
       </c>
       <c s="4" r="W10">
-        <v>4780.16</v>
+        <v>9487.55</v>
       </c>
       <c s="5" t="str" r="X10"/>
     </row>
@@ -1140,32 +1140,32 @@
       </c>
       <c s="3" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">6145554</t>
+          <t xml:space="preserve">6142940</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D11">
         <is>
-          <t xml:space="preserve">MOZAİK GIDA-ALAZI</t>
+          <t xml:space="preserve">SİBELA SÜPERMAKET AŞAĞIOKÇULAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">37356</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">SERAY AKSOY</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">11446</t>
+          <t xml:space="preserve">11824</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">PET FRK GAZOZ 1.5L 12X 20KCAL DRS</t>
+          <t xml:space="preserve">PET LIP MANGO 1.5L 6X SIRENADRS</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I11">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c s="4" r="L11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c s="4" r="M11">
         <v>0</v>
@@ -1193,31 +1193,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O11">
-        <v>37.86</v>
+        <v>47.50</v>
       </c>
       <c s="4" r="P11">
-        <v>1441.44</v>
+        <v>1985.10</v>
       </c>
       <c s="4" r="Q11">
-        <v>0</v>
+        <v>29.89</v>
       </c>
       <c s="4" r="R11">
-        <v>378.48</v>
+        <v>490.52</v>
       </c>
       <c s="4" r="S11">
         <v>0</v>
       </c>
       <c s="4" r="T11">
-        <v>378.48</v>
+        <v>520.41</v>
       </c>
       <c s="4" r="U11">
-        <v>1062.96</v>
+        <v>1464.69</v>
       </c>
       <c s="4" r="V11">
-        <v>106.30</v>
+        <v>146.47</v>
       </c>
       <c s="4" r="W11">
-        <v>1169.26</v>
+        <v>1611.16</v>
       </c>
       <c s="5" t="str" r="X11"/>
     </row>
@@ -1234,32 +1234,32 @@
       </c>
       <c s="3" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">6145554</t>
+          <t xml:space="preserve">6142940</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D12">
         <is>
-          <t xml:space="preserve">MOZAİK GIDA-ALAZI</t>
+          <t xml:space="preserve">SİBELA SÜPERMAKET AŞAĞIOKÇULAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">37356</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">SERAY AKSOY</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G12">
         <is>
-          <t xml:space="preserve">11543</t>
+          <t xml:space="preserve">11488</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
+          <t xml:space="preserve">PET LIP MANGO 1L 6X DRS</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I12">
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c s="4" r="L12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c s="4" r="M12">
         <v>0</v>
@@ -1287,31 +1287,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O12">
-        <v>47.40</v>
+        <v>32.00</v>
       </c>
       <c s="4" r="P12">
-        <v>1242</v>
+        <v>1602.30</v>
       </c>
       <c s="4" r="Q12">
-        <v>0</v>
+        <v>25.80</v>
       </c>
       <c s="4" r="R12">
-        <v>363.42</v>
+        <v>312.45</v>
       </c>
       <c s="4" r="S12">
         <v>0</v>
       </c>
       <c s="4" r="T12">
-        <v>363.42</v>
+        <v>338.25</v>
       </c>
       <c s="4" r="U12">
-        <v>878.58</v>
+        <v>1264.05</v>
       </c>
       <c s="4" r="V12">
-        <v>87.86</v>
+        <v>126.41</v>
       </c>
       <c s="4" r="W12">
-        <v>966.44</v>
+        <v>1390.46</v>
       </c>
       <c s="5" t="str" r="X12"/>
     </row>
@@ -1328,32 +1328,32 @@
       </c>
       <c s="3" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">6145554</t>
+          <t xml:space="preserve">6142940</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D13">
         <is>
-          <t xml:space="preserve">MOZAİK GIDA-ALAZI</t>
+          <t xml:space="preserve">SİBELA SÜPERMAKET AŞAĞIOKÇULAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">37356</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">SERAY AKSOY</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G13">
         <is>
-          <t xml:space="preserve">11452</t>
+          <t xml:space="preserve">11675</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">PET PC KOLA 2.5L 6X 100KCAL DRS</t>
+          <t xml:space="preserve">PET LIP SEFT 1.5L 6X ROMANYA</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I13">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c s="4" r="L13">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c s="4" r="M13">
         <v>0</v>
@@ -1381,31 +1381,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O13">
-        <v>400.00</v>
+        <v>47.05</v>
       </c>
       <c s="4" r="P13">
-        <v>12223.50</v>
+        <v>1985.10</v>
       </c>
       <c s="4" r="Q13">
-        <v>0</v>
+        <v>29.89</v>
       </c>
       <c s="4" r="R13">
-        <v>3140.33</v>
+        <v>490.52</v>
       </c>
       <c s="4" r="S13">
         <v>0</v>
       </c>
       <c s="4" r="T13">
-        <v>3140.33</v>
+        <v>520.41</v>
       </c>
       <c s="4" r="U13">
-        <v>9083.17</v>
+        <v>1464.69</v>
       </c>
       <c s="4" r="V13">
-        <v>908.32</v>
+        <v>146.47</v>
       </c>
       <c s="4" r="W13">
-        <v>9991.49</v>
+        <v>1611.16</v>
       </c>
       <c s="5" t="str" r="X13"/>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c s="3" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">5299770</t>
+          <t xml:space="preserve">6142940</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D14">
         <is>
-          <t xml:space="preserve">TAHSİN MİRİOĞLU</t>
+          <t xml:space="preserve">SİBELA SÜPERMAKET AŞAĞIOKÇULAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E14">
@@ -1442,17 +1442,17 @@
       </c>
       <c s="3" t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">11743</t>
+          <t xml:space="preserve">11515</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">PET PC KOLA 1.5L 12X 70KCAL</t>
+          <t xml:space="preserve">PET LIP SEFT 1L 6X SIRENA DRS</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I14">
         <is>
-          <t xml:space="preserve">126883</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="3" t="inlineStr" r="J14">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c s="4" r="L14">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c s="4" r="M14">
         <v>0</v>
@@ -1475,31 +1475,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O14">
-        <v>3859.92</v>
+        <v>32.50</v>
       </c>
       <c s="4" r="P14">
-        <v>141120</v>
+        <v>1602.30</v>
       </c>
       <c s="4" r="Q14">
-        <v>0</v>
+        <v>25.80</v>
       </c>
       <c s="4" r="R14">
-        <v>35661.02</v>
+        <v>312.45</v>
       </c>
       <c s="4" r="S14">
         <v>0</v>
       </c>
       <c s="4" r="T14">
-        <v>35661.02</v>
+        <v>338.25</v>
       </c>
       <c s="4" r="U14">
-        <v>105458.98</v>
+        <v>1264.05</v>
       </c>
       <c s="4" r="V14">
-        <v>10545.90</v>
+        <v>126.41</v>
       </c>
       <c s="4" r="W14">
-        <v>116004.87</v>
+        <v>1390.46</v>
       </c>
       <c s="5" t="str" r="X14"/>
     </row>
@@ -1516,32 +1516,32 @@
       </c>
       <c s="3" t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">5678767</t>
+          <t xml:space="preserve">6142940</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D15">
         <is>
-          <t xml:space="preserve">ÖZLEM MARKET BATUHAN ALBAYRAK</t>
+          <t xml:space="preserve">SİBELA SÜPERMAKET AŞAĞIOKÇULAR</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">11996</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">ABDULGANİ GÜLER</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">11452</t>
+          <t xml:space="preserve">11952</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">PET PC KOLA 2.5L 6X 100KCAL DRS</t>
+          <t xml:space="preserve">PET LIP SPARK LIM YUZU 1L 4X</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I15">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c s="4" r="L15">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c s="4" r="M15">
         <v>0</v>
@@ -1569,31 +1569,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O15">
-        <v>320.00</v>
+        <v>4.20</v>
       </c>
       <c s="4" r="P15">
-        <v>9778.80</v>
+        <v>213.64</v>
       </c>
       <c s="4" r="Q15">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c s="4" r="R15">
-        <v>2512.26</v>
+        <v>27.67</v>
       </c>
       <c s="4" r="S15">
         <v>0</v>
       </c>
       <c s="4" r="T15">
-        <v>2512.26</v>
+        <v>31.39</v>
       </c>
       <c s="4" r="U15">
-        <v>7266.54</v>
+        <v>182.25</v>
       </c>
       <c s="4" r="V15">
-        <v>726.65</v>
+        <v>18.23</v>
       </c>
       <c s="4" r="W15">
-        <v>7993.19</v>
+        <v>200.48</v>
       </c>
       <c s="5" t="str" r="X15"/>
     </row>
@@ -1610,32 +1610,32 @@
       </c>
       <c s="3" t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">5678767</t>
+          <t xml:space="preserve">6107051</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D16">
         <is>
-          <t xml:space="preserve">ÖZLEM MARKET BATUHAN ALBAYRAK</t>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E16">
         <is>
-          <t xml:space="preserve">11996</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">ABDULGANİ GÜLER</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G16">
         <is>
-          <t xml:space="preserve">11982</t>
+          <t xml:space="preserve">11845</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">PET PC MAX KOLA 1L 12X BANTLAMA BEDELSIZ</t>
+          <t xml:space="preserve">CAN STNG KIR MEY 500ML 12X</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="I16">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c s="4" r="L16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="4" r="M16">
         <v>0</v>
@@ -1663,31 +1663,31 @@
         <v>0</v>
       </c>
       <c s="4" r="O16">
-        <v>12.70</v>
+        <v>8.43</v>
       </c>
       <c s="4" r="P16">
-        <v>0.00</v>
+        <v>1083.12</v>
       </c>
       <c s="4" r="Q16">
         <v>0</v>
       </c>
       <c s="4" r="R16">
-        <v>0.00</v>
+        <v>400.75</v>
       </c>
       <c s="4" r="S16">
         <v>0</v>
       </c>
       <c s="4" r="T16">
-        <v>0.00</v>
+        <v>400.75</v>
       </c>
       <c s="4" r="U16">
-        <v>0.00</v>
+        <v>682.37</v>
       </c>
       <c s="4" r="V16">
-        <v>0.00</v>
+        <v>68.24</v>
       </c>
       <c s="4" r="W16">
-        <v>0.00</v>
+        <v>750.60</v>
       </c>
       <c s="5" t="str" r="X16"/>
     </row>
@@ -1704,158 +1704,6361 @@
       </c>
       <c s="3" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">5678767</t>
+          <t xml:space="preserve">6107051</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="D17">
         <is>
-          <t xml:space="preserve">ÖZLEM MARKET BATUHAN ALBAYRAK</t>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">11996</t>
+          <t xml:space="preserve">28153</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="F17">
         <is>
-          <t xml:space="preserve">ABDULGANİ GÜLER</t>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
         </is>
       </c>
       <c s="3" t="inlineStr" r="G17">
         <is>
+          <t xml:space="preserve">11543</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H17">
+        <is>
+          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I17">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J17">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K17">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L17">
+        <v>32</v>
+      </c>
+      <c s="4" r="M17">
+        <v>0</v>
+      </c>
+      <c s="4" r="N17">
+        <v>0</v>
+      </c>
+      <c s="4" r="O17">
+        <v>505.59</v>
+      </c>
+      <c s="4" r="P17">
+        <v>12024.96</v>
+      </c>
+      <c s="4" r="Q17">
+        <v>176.02</v>
+      </c>
+      <c s="4" r="R17">
+        <v>3223.89</v>
+      </c>
+      <c s="4" r="S17">
+        <v>0</v>
+      </c>
+      <c s="4" r="T17">
+        <v>3399.91</v>
+      </c>
+      <c s="4" r="U17">
+        <v>8625.05</v>
+      </c>
+      <c s="4" r="V17">
+        <v>862.50</v>
+      </c>
+      <c s="4" r="W17">
+        <v>9487.55</v>
+      </c>
+      <c s="5" t="str" r="X17"/>
+    </row>
+    <row r="18" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A18">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C18">
+        <is>
+          <t xml:space="preserve">6107051</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D18">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E18">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F18">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G18">
+        <is>
+          <t xml:space="preserve">11490</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H18">
+        <is>
+          <t xml:space="preserve">PET LIP KRP NANE 1L 6X SIRENA NEW DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I18">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J18">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K18">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L18">
+        <v>10</v>
+      </c>
+      <c s="4" r="M18">
+        <v>0</v>
+      </c>
+      <c s="4" r="N18">
+        <v>0</v>
+      </c>
+      <c s="4" r="O18">
+        <v>65.00</v>
+      </c>
+      <c s="4" r="P18">
+        <v>3204.60</v>
+      </c>
+      <c s="4" r="Q18">
+        <v>51.59</v>
+      </c>
+      <c s="4" r="R18">
+        <v>624.90</v>
+      </c>
+      <c s="4" r="S18">
+        <v>0</v>
+      </c>
+      <c s="4" r="T18">
+        <v>676.49</v>
+      </c>
+      <c s="4" r="U18">
+        <v>2528.11</v>
+      </c>
+      <c s="4" r="V18">
+        <v>252.81</v>
+      </c>
+      <c s="4" r="W18">
+        <v>2780.92</v>
+      </c>
+      <c s="5" t="str" r="X18"/>
+    </row>
+    <row r="19" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A19">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C19">
+        <is>
+          <t xml:space="preserve">6107051</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D19">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E19">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F19">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G19">
+        <is>
+          <t xml:space="preserve">11486</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H19">
+        <is>
+          <t xml:space="preserve">PET LIP LIM 1L 6X SIRENA NEW FP DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I19">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J19">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K19">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L19">
+        <v>10</v>
+      </c>
+      <c s="4" r="M19">
+        <v>0</v>
+      </c>
+      <c s="4" r="N19">
+        <v>0</v>
+      </c>
+      <c s="4" r="O19">
+        <v>65.00</v>
+      </c>
+      <c s="4" r="P19">
+        <v>3204.60</v>
+      </c>
+      <c s="4" r="Q19">
+        <v>51.59</v>
+      </c>
+      <c s="4" r="R19">
+        <v>624.90</v>
+      </c>
+      <c s="4" r="S19">
+        <v>0</v>
+      </c>
+      <c s="4" r="T19">
+        <v>676.49</v>
+      </c>
+      <c s="4" r="U19">
+        <v>2528.11</v>
+      </c>
+      <c s="4" r="V19">
+        <v>252.81</v>
+      </c>
+      <c s="4" r="W19">
+        <v>2780.92</v>
+      </c>
+      <c s="5" t="str" r="X19"/>
+    </row>
+    <row r="20" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A20">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C20">
+        <is>
+          <t xml:space="preserve">6107051</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D20">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F20">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G20">
+        <is>
+          <t xml:space="preserve">11824</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H20">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1.5L 6X SIRENADRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I20">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J20">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K20">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L20">
+        <v>5</v>
+      </c>
+      <c s="4" r="M20">
+        <v>0</v>
+      </c>
+      <c s="4" r="N20">
+        <v>0</v>
+      </c>
+      <c s="4" r="O20">
+        <v>47.50</v>
+      </c>
+      <c s="4" r="P20">
+        <v>1985.10</v>
+      </c>
+      <c s="4" r="Q20">
+        <v>29.89</v>
+      </c>
+      <c s="4" r="R20">
+        <v>490.52</v>
+      </c>
+      <c s="4" r="S20">
+        <v>0</v>
+      </c>
+      <c s="4" r="T20">
+        <v>520.41</v>
+      </c>
+      <c s="4" r="U20">
+        <v>1464.69</v>
+      </c>
+      <c s="4" r="V20">
+        <v>146.47</v>
+      </c>
+      <c s="4" r="W20">
+        <v>1611.16</v>
+      </c>
+      <c s="5" t="str" r="X20"/>
+    </row>
+    <row r="21" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A21">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">6107051</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D21">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E21">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F21">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G21">
+        <is>
+          <t xml:space="preserve">11488</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H21">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1L 6X DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I21">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J21">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K21">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L21">
+        <v>10</v>
+      </c>
+      <c s="4" r="M21">
+        <v>0</v>
+      </c>
+      <c s="4" r="N21">
+        <v>0</v>
+      </c>
+      <c s="4" r="O21">
+        <v>64.00</v>
+      </c>
+      <c s="4" r="P21">
+        <v>3204.60</v>
+      </c>
+      <c s="4" r="Q21">
+        <v>51.59</v>
+      </c>
+      <c s="4" r="R21">
+        <v>624.90</v>
+      </c>
+      <c s="4" r="S21">
+        <v>0</v>
+      </c>
+      <c s="4" r="T21">
+        <v>676.49</v>
+      </c>
+      <c s="4" r="U21">
+        <v>2528.11</v>
+      </c>
+      <c s="4" r="V21">
+        <v>252.81</v>
+      </c>
+      <c s="4" r="W21">
+        <v>2780.92</v>
+      </c>
+      <c s="5" t="str" r="X21"/>
+    </row>
+    <row r="22" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A22">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">6107051</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D22">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E22">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F22">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G22">
+        <is>
+          <t xml:space="preserve">11675</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H22">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1.5L 6X ROMANYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I22">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J22">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K22">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L22">
+        <v>5</v>
+      </c>
+      <c s="4" r="M22">
+        <v>0</v>
+      </c>
+      <c s="4" r="N22">
+        <v>0</v>
+      </c>
+      <c s="4" r="O22">
+        <v>47.05</v>
+      </c>
+      <c s="4" r="P22">
+        <v>1985.10</v>
+      </c>
+      <c s="4" r="Q22">
+        <v>29.89</v>
+      </c>
+      <c s="4" r="R22">
+        <v>490.52</v>
+      </c>
+      <c s="4" r="S22">
+        <v>0</v>
+      </c>
+      <c s="4" r="T22">
+        <v>520.41</v>
+      </c>
+      <c s="4" r="U22">
+        <v>1464.69</v>
+      </c>
+      <c s="4" r="V22">
+        <v>146.47</v>
+      </c>
+      <c s="4" r="W22">
+        <v>1611.16</v>
+      </c>
+      <c s="5" t="str" r="X22"/>
+    </row>
+    <row r="23" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A23">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">6107051</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D23">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E23">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F23">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G23">
+        <is>
+          <t xml:space="preserve">11515</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H23">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1L 6X SIRENA DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I23">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J23">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K23">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L23">
+        <v>10</v>
+      </c>
+      <c s="4" r="M23">
+        <v>0</v>
+      </c>
+      <c s="4" r="N23">
+        <v>0</v>
+      </c>
+      <c s="4" r="O23">
+        <v>65.00</v>
+      </c>
+      <c s="4" r="P23">
+        <v>3204.60</v>
+      </c>
+      <c s="4" r="Q23">
+        <v>51.59</v>
+      </c>
+      <c s="4" r="R23">
+        <v>624.90</v>
+      </c>
+      <c s="4" r="S23">
+        <v>0</v>
+      </c>
+      <c s="4" r="T23">
+        <v>676.49</v>
+      </c>
+      <c s="4" r="U23">
+        <v>2528.11</v>
+      </c>
+      <c s="4" r="V23">
+        <v>252.81</v>
+      </c>
+      <c s="4" r="W23">
+        <v>2780.92</v>
+      </c>
+      <c s="5" t="str" r="X23"/>
+    </row>
+    <row r="24" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A24">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">6107051</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D24">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET GIDA SAN.TİC.LTD.ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E24">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F24">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G24">
+        <is>
+          <t xml:space="preserve">11952</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H24">
+        <is>
+          <t xml:space="preserve">PET LIP SPARK LIM YUZU 1L 4X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I24">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J24">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K24">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L24">
+        <v>6</v>
+      </c>
+      <c s="4" r="M24">
+        <v>0</v>
+      </c>
+      <c s="4" r="N24">
+        <v>0</v>
+      </c>
+      <c s="4" r="O24">
+        <v>25.20</v>
+      </c>
+      <c s="4" r="P24">
+        <v>1281.84</v>
+      </c>
+      <c s="4" r="Q24">
+        <v>17.81</v>
+      </c>
+      <c s="4" r="R24">
+        <v>391.35</v>
+      </c>
+      <c s="4" r="S24">
+        <v>0</v>
+      </c>
+      <c s="4" r="T24">
+        <v>409.16</v>
+      </c>
+      <c s="4" r="U24">
+        <v>872.68</v>
+      </c>
+      <c s="4" r="V24">
+        <v>87.27</v>
+      </c>
+      <c s="4" r="W24">
+        <v>959.95</v>
+      </c>
+      <c s="5" t="str" r="X24"/>
+    </row>
+    <row r="25" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A25">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">6115936</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D25">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET KUZEYTEPE</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E25">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F25">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G25">
+        <is>
+          <t xml:space="preserve">11845</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H25">
+        <is>
+          <t xml:space="preserve">CAN STNG KIR MEY 500ML 12X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I25">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J25">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K25">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L25">
+        <v>2</v>
+      </c>
+      <c s="4" r="M25">
+        <v>0</v>
+      </c>
+      <c s="4" r="N25">
+        <v>0</v>
+      </c>
+      <c s="4" r="O25">
+        <v>8.43</v>
+      </c>
+      <c s="4" r="P25">
+        <v>1083.12</v>
+      </c>
+      <c s="4" r="Q25">
+        <v>0</v>
+      </c>
+      <c s="4" r="R25">
+        <v>400.75</v>
+      </c>
+      <c s="4" r="S25">
+        <v>0</v>
+      </c>
+      <c s="4" r="T25">
+        <v>400.75</v>
+      </c>
+      <c s="4" r="U25">
+        <v>682.37</v>
+      </c>
+      <c s="4" r="V25">
+        <v>68.24</v>
+      </c>
+      <c s="4" r="W25">
+        <v>750.60</v>
+      </c>
+      <c s="5" t="str" r="X25"/>
+    </row>
+    <row r="26" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A26">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">6115936</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D26">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET KUZEYTEPE</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E26">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F26">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G26">
+        <is>
+          <t xml:space="preserve">11543</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H26">
+        <is>
+          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I26">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J26">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K26">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L26">
+        <v>32</v>
+      </c>
+      <c s="4" r="M26">
+        <v>0</v>
+      </c>
+      <c s="4" r="N26">
+        <v>0</v>
+      </c>
+      <c s="4" r="O26">
+        <v>505.59</v>
+      </c>
+      <c s="4" r="P26">
+        <v>12024.96</v>
+      </c>
+      <c s="4" r="Q26">
+        <v>176.02</v>
+      </c>
+      <c s="4" r="R26">
+        <v>3223.89</v>
+      </c>
+      <c s="4" r="S26">
+        <v>0</v>
+      </c>
+      <c s="4" r="T26">
+        <v>3399.91</v>
+      </c>
+      <c s="4" r="U26">
+        <v>8625.05</v>
+      </c>
+      <c s="4" r="V26">
+        <v>862.50</v>
+      </c>
+      <c s="4" r="W26">
+        <v>9487.55</v>
+      </c>
+      <c s="5" t="str" r="X26"/>
+    </row>
+    <row r="27" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A27">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">6115936</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D27">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET KUZEYTEPE</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E27">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F27">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G27">
+        <is>
+          <t xml:space="preserve">11824</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H27">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1.5L 6X SIRENADRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I27">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J27">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K27">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L27">
+        <v>5</v>
+      </c>
+      <c s="4" r="M27">
+        <v>0</v>
+      </c>
+      <c s="4" r="N27">
+        <v>0</v>
+      </c>
+      <c s="4" r="O27">
+        <v>47.50</v>
+      </c>
+      <c s="4" r="P27">
+        <v>1985.10</v>
+      </c>
+      <c s="4" r="Q27">
+        <v>29.89</v>
+      </c>
+      <c s="4" r="R27">
+        <v>490.52</v>
+      </c>
+      <c s="4" r="S27">
+        <v>0</v>
+      </c>
+      <c s="4" r="T27">
+        <v>520.41</v>
+      </c>
+      <c s="4" r="U27">
+        <v>1464.69</v>
+      </c>
+      <c s="4" r="V27">
+        <v>146.47</v>
+      </c>
+      <c s="4" r="W27">
+        <v>1611.16</v>
+      </c>
+      <c s="5" t="str" r="X27"/>
+    </row>
+    <row r="28" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A28">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">6115936</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D28">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET KUZEYTEPE</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E28">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F28">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G28">
+        <is>
+          <t xml:space="preserve">11488</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H28">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1L 6X DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I28">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J28">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K28">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L28">
+        <v>5</v>
+      </c>
+      <c s="4" r="M28">
+        <v>0</v>
+      </c>
+      <c s="4" r="N28">
+        <v>0</v>
+      </c>
+      <c s="4" r="O28">
+        <v>32.00</v>
+      </c>
+      <c s="4" r="P28">
+        <v>1602.30</v>
+      </c>
+      <c s="4" r="Q28">
+        <v>25.80</v>
+      </c>
+      <c s="4" r="R28">
+        <v>312.45</v>
+      </c>
+      <c s="4" r="S28">
+        <v>0</v>
+      </c>
+      <c s="4" r="T28">
+        <v>338.25</v>
+      </c>
+      <c s="4" r="U28">
+        <v>1264.05</v>
+      </c>
+      <c s="4" r="V28">
+        <v>126.41</v>
+      </c>
+      <c s="4" r="W28">
+        <v>1390.46</v>
+      </c>
+      <c s="5" t="str" r="X28"/>
+    </row>
+    <row r="29" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A29">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C29">
+        <is>
+          <t xml:space="preserve">6115936</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D29">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET KUZEYTEPE</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E29">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F29">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G29">
+        <is>
+          <t xml:space="preserve">11675</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H29">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1.5L 6X ROMANYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I29">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J29">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K29">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L29">
+        <v>5</v>
+      </c>
+      <c s="4" r="M29">
+        <v>0</v>
+      </c>
+      <c s="4" r="N29">
+        <v>0</v>
+      </c>
+      <c s="4" r="O29">
+        <v>47.05</v>
+      </c>
+      <c s="4" r="P29">
+        <v>1985.10</v>
+      </c>
+      <c s="4" r="Q29">
+        <v>29.89</v>
+      </c>
+      <c s="4" r="R29">
+        <v>490.52</v>
+      </c>
+      <c s="4" r="S29">
+        <v>0</v>
+      </c>
+      <c s="4" r="T29">
+        <v>520.41</v>
+      </c>
+      <c s="4" r="U29">
+        <v>1464.69</v>
+      </c>
+      <c s="4" r="V29">
+        <v>146.47</v>
+      </c>
+      <c s="4" r="W29">
+        <v>1611.16</v>
+      </c>
+      <c s="5" t="str" r="X29"/>
+    </row>
+    <row r="30" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A30">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">6115936</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D30">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET KUZEYTEPE</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E30">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F30">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G30">
+        <is>
+          <t xml:space="preserve">11515</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H30">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1L 6X SIRENA DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I30">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J30">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K30">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L30">
+        <v>5</v>
+      </c>
+      <c s="4" r="M30">
+        <v>0</v>
+      </c>
+      <c s="4" r="N30">
+        <v>0</v>
+      </c>
+      <c s="4" r="O30">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P30">
+        <v>1602.30</v>
+      </c>
+      <c s="4" r="Q30">
+        <v>25.80</v>
+      </c>
+      <c s="4" r="R30">
+        <v>312.45</v>
+      </c>
+      <c s="4" r="S30">
+        <v>0</v>
+      </c>
+      <c s="4" r="T30">
+        <v>338.25</v>
+      </c>
+      <c s="4" r="U30">
+        <v>1264.05</v>
+      </c>
+      <c s="4" r="V30">
+        <v>126.41</v>
+      </c>
+      <c s="4" r="W30">
+        <v>1390.46</v>
+      </c>
+      <c s="5" t="str" r="X30"/>
+    </row>
+    <row r="31" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A31">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">6115936</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D31">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET KUZEYTEPE</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E31">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F31">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G31">
+        <is>
+          <t xml:space="preserve">11952</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H31">
+        <is>
+          <t xml:space="preserve">PET LIP SPARK LIM YUZU 1L 4X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I31">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J31">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K31">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L31">
+        <v>2</v>
+      </c>
+      <c s="4" r="M31">
+        <v>0</v>
+      </c>
+      <c s="4" r="N31">
+        <v>0</v>
+      </c>
+      <c s="4" r="O31">
+        <v>8.40</v>
+      </c>
+      <c s="4" r="P31">
+        <v>427.28</v>
+      </c>
+      <c s="4" r="Q31">
+        <v>6.88</v>
+      </c>
+      <c s="4" r="R31">
+        <v>83.32</v>
+      </c>
+      <c s="4" r="S31">
+        <v>0</v>
+      </c>
+      <c s="4" r="T31">
+        <v>90.20</v>
+      </c>
+      <c s="4" r="U31">
+        <v>337.08</v>
+      </c>
+      <c s="4" r="V31">
+        <v>33.71</v>
+      </c>
+      <c s="4" r="W31">
+        <v>370.79</v>
+      </c>
+      <c s="5" t="str" r="X31"/>
+    </row>
+    <row r="32" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A32">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C32">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D32">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E32">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F32">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G32">
+        <is>
+          <t xml:space="preserve">11845</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H32">
+        <is>
+          <t xml:space="preserve">CAN STNG KIR MEY 500ML 12X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I32">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J32">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K32">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L32">
+        <v>4</v>
+      </c>
+      <c s="4" r="M32">
+        <v>0</v>
+      </c>
+      <c s="4" r="N32">
+        <v>0</v>
+      </c>
+      <c s="4" r="O32">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P32">
+        <v>2166.24</v>
+      </c>
+      <c s="4" r="Q32">
+        <v>0</v>
+      </c>
+      <c s="4" r="R32">
+        <v>801.51</v>
+      </c>
+      <c s="4" r="S32">
+        <v>0</v>
+      </c>
+      <c s="4" r="T32">
+        <v>801.51</v>
+      </c>
+      <c s="4" r="U32">
+        <v>1364.73</v>
+      </c>
+      <c s="4" r="V32">
+        <v>136.47</v>
+      </c>
+      <c s="4" r="W32">
+        <v>1501.20</v>
+      </c>
+      <c s="5" t="str" r="X32"/>
+    </row>
+    <row r="33" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A33">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B33">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C33">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D33">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E33">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F33">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G33">
+        <is>
+          <t xml:space="preserve">11543</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H33">
+        <is>
+          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I33">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J33">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K33">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L33">
+        <v>32</v>
+      </c>
+      <c s="4" r="M33">
+        <v>0</v>
+      </c>
+      <c s="4" r="N33">
+        <v>0</v>
+      </c>
+      <c s="4" r="O33">
+        <v>505.59</v>
+      </c>
+      <c s="4" r="P33">
+        <v>12024.96</v>
+      </c>
+      <c s="4" r="Q33">
+        <v>176.02</v>
+      </c>
+      <c s="4" r="R33">
+        <v>3223.89</v>
+      </c>
+      <c s="4" r="S33">
+        <v>0</v>
+      </c>
+      <c s="4" r="T33">
+        <v>3399.91</v>
+      </c>
+      <c s="4" r="U33">
+        <v>8625.05</v>
+      </c>
+      <c s="4" r="V33">
+        <v>862.50</v>
+      </c>
+      <c s="4" r="W33">
+        <v>9487.55</v>
+      </c>
+      <c s="5" t="str" r="X33"/>
+    </row>
+    <row r="34" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A34">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C34">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D34">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E34">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F34">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G34">
+        <is>
+          <t xml:space="preserve">11822</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H34">
+        <is>
+          <t xml:space="preserve">PET LIP KRP NANE 1.5L 6X SIRENADRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I34">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J34">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K34">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L34">
+        <v>25</v>
+      </c>
+      <c s="4" r="M34">
+        <v>0</v>
+      </c>
+      <c s="4" r="N34">
+        <v>0</v>
+      </c>
+      <c s="4" r="O34">
+        <v>237.50</v>
+      </c>
+      <c s="4" r="P34">
+        <v>9925.50</v>
+      </c>
+      <c s="4" r="Q34">
+        <v>164.56</v>
+      </c>
+      <c s="4" r="R34">
+        <v>1697.26</v>
+      </c>
+      <c s="4" r="S34">
+        <v>0</v>
+      </c>
+      <c s="4" r="T34">
+        <v>1861.83</v>
+      </c>
+      <c s="4" r="U34">
+        <v>8063.67</v>
+      </c>
+      <c s="4" r="V34">
+        <v>806.37</v>
+      </c>
+      <c s="4" r="W34">
+        <v>8870.04</v>
+      </c>
+      <c s="5" t="str" r="X34"/>
+    </row>
+    <row r="35" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A35">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B35">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C35">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D35">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E35">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F35">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G35">
+        <is>
+          <t xml:space="preserve">11823</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H35">
+        <is>
+          <t xml:space="preserve">PET LIP LIM 1.5L 6X SIRENA NEWFP DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I35">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J35">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K35">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L35">
+        <v>10</v>
+      </c>
+      <c s="4" r="M35">
+        <v>0</v>
+      </c>
+      <c s="4" r="N35">
+        <v>0</v>
+      </c>
+      <c s="4" r="O35">
+        <v>95.00</v>
+      </c>
+      <c s="4" r="P35">
+        <v>3970.20</v>
+      </c>
+      <c s="4" r="Q35">
+        <v>65.83</v>
+      </c>
+      <c s="4" r="R35">
+        <v>678.90</v>
+      </c>
+      <c s="4" r="S35">
+        <v>0</v>
+      </c>
+      <c s="4" r="T35">
+        <v>744.73</v>
+      </c>
+      <c s="4" r="U35">
+        <v>3225.47</v>
+      </c>
+      <c s="4" r="V35">
+        <v>322.55</v>
+      </c>
+      <c s="4" r="W35">
+        <v>3548.02</v>
+      </c>
+      <c s="5" t="str" r="X35"/>
+    </row>
+    <row r="36" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A36">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B36">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C36">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D36">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E36">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F36">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G36">
+        <is>
+          <t xml:space="preserve">11824</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H36">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1.5L 6X SIRENADRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I36">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J36">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K36">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L36">
+        <v>5</v>
+      </c>
+      <c s="4" r="M36">
+        <v>0</v>
+      </c>
+      <c s="4" r="N36">
+        <v>0</v>
+      </c>
+      <c s="4" r="O36">
+        <v>47.50</v>
+      </c>
+      <c s="4" r="P36">
+        <v>1985.10</v>
+      </c>
+      <c s="4" r="Q36">
+        <v>29.89</v>
+      </c>
+      <c s="4" r="R36">
+        <v>490.52</v>
+      </c>
+      <c s="4" r="S36">
+        <v>0</v>
+      </c>
+      <c s="4" r="T36">
+        <v>520.41</v>
+      </c>
+      <c s="4" r="U36">
+        <v>1464.69</v>
+      </c>
+      <c s="4" r="V36">
+        <v>146.47</v>
+      </c>
+      <c s="4" r="W36">
+        <v>1611.16</v>
+      </c>
+      <c s="5" t="str" r="X36"/>
+    </row>
+    <row r="37" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A37">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B37">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C37">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D37">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E37">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F37">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G37">
+        <is>
+          <t xml:space="preserve">11488</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H37">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1L 6X DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I37">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J37">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K37">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L37">
+        <v>5</v>
+      </c>
+      <c s="4" r="M37">
+        <v>0</v>
+      </c>
+      <c s="4" r="N37">
+        <v>0</v>
+      </c>
+      <c s="4" r="O37">
+        <v>32.00</v>
+      </c>
+      <c s="4" r="P37">
+        <v>1602.30</v>
+      </c>
+      <c s="4" r="Q37">
+        <v>25.80</v>
+      </c>
+      <c s="4" r="R37">
+        <v>312.45</v>
+      </c>
+      <c s="4" r="S37">
+        <v>0</v>
+      </c>
+      <c s="4" r="T37">
+        <v>338.25</v>
+      </c>
+      <c s="4" r="U37">
+        <v>1264.05</v>
+      </c>
+      <c s="4" r="V37">
+        <v>126.41</v>
+      </c>
+      <c s="4" r="W37">
+        <v>1390.46</v>
+      </c>
+      <c s="5" t="str" r="X37"/>
+    </row>
+    <row r="38" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A38">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B38">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C38">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D38">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E38">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F38">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G38">
+        <is>
+          <t xml:space="preserve">11675</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H38">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1.5L 6X ROMANYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I38">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J38">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K38">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L38">
+        <v>10</v>
+      </c>
+      <c s="4" r="M38">
+        <v>0</v>
+      </c>
+      <c s="4" r="N38">
+        <v>0</v>
+      </c>
+      <c s="4" r="O38">
+        <v>94.10</v>
+      </c>
+      <c s="4" r="P38">
+        <v>3970.20</v>
+      </c>
+      <c s="4" r="Q38">
+        <v>59.78</v>
+      </c>
+      <c s="4" r="R38">
+        <v>981.04</v>
+      </c>
+      <c s="4" r="S38">
+        <v>0</v>
+      </c>
+      <c s="4" r="T38">
+        <v>1040.82</v>
+      </c>
+      <c s="4" r="U38">
+        <v>2929.38</v>
+      </c>
+      <c s="4" r="V38">
+        <v>292.94</v>
+      </c>
+      <c s="4" r="W38">
+        <v>3222.32</v>
+      </c>
+      <c s="5" t="str" r="X38"/>
+    </row>
+    <row r="39" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A39">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B39">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C39">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D39">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E39">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F39">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G39">
+        <is>
+          <t xml:space="preserve">11515</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H39">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1L 6X SIRENA DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I39">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J39">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K39">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L39">
+        <v>5</v>
+      </c>
+      <c s="4" r="M39">
+        <v>0</v>
+      </c>
+      <c s="4" r="N39">
+        <v>0</v>
+      </c>
+      <c s="4" r="O39">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P39">
+        <v>1602.30</v>
+      </c>
+      <c s="4" r="Q39">
+        <v>25.80</v>
+      </c>
+      <c s="4" r="R39">
+        <v>312.45</v>
+      </c>
+      <c s="4" r="S39">
+        <v>0</v>
+      </c>
+      <c s="4" r="T39">
+        <v>338.25</v>
+      </c>
+      <c s="4" r="U39">
+        <v>1264.05</v>
+      </c>
+      <c s="4" r="V39">
+        <v>126.41</v>
+      </c>
+      <c s="4" r="W39">
+        <v>1390.46</v>
+      </c>
+      <c s="5" t="str" r="X39"/>
+    </row>
+    <row r="40" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A40">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B40">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C40">
+        <is>
+          <t xml:space="preserve">6115939</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D40">
+        <is>
+          <t xml:space="preserve">SİBELA SÜPERMARKET ZÜLÜFLÜHAN</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E40">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F40">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G40">
+        <is>
+          <t xml:space="preserve">11952</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H40">
+        <is>
+          <t xml:space="preserve">PET LIP SPARK LIM YUZU 1L 4X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I40">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J40">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K40">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L40">
+        <v>6</v>
+      </c>
+      <c s="4" r="M40">
+        <v>0</v>
+      </c>
+      <c s="4" r="N40">
+        <v>0</v>
+      </c>
+      <c s="4" r="O40">
+        <v>25.20</v>
+      </c>
+      <c s="4" r="P40">
+        <v>1281.84</v>
+      </c>
+      <c s="4" r="Q40">
+        <v>17.81</v>
+      </c>
+      <c s="4" r="R40">
+        <v>391.35</v>
+      </c>
+      <c s="4" r="S40">
+        <v>0</v>
+      </c>
+      <c s="4" r="T40">
+        <v>409.16</v>
+      </c>
+      <c s="4" r="U40">
+        <v>872.68</v>
+      </c>
+      <c s="4" r="V40">
+        <v>87.27</v>
+      </c>
+      <c s="4" r="W40">
+        <v>959.95</v>
+      </c>
+      <c s="5" t="str" r="X40"/>
+    </row>
+    <row r="41" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A41">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B41">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C41">
+        <is>
+          <t xml:space="preserve">5505689</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D41">
+        <is>
+          <t xml:space="preserve">SİDAL SPOT</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E41">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F41">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G41">
+        <is>
+          <t xml:space="preserve">11813</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H41">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I41">
+        <is>
+          <t xml:space="preserve">848691</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J41">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K41">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L41">
+        <v>300</v>
+      </c>
+      <c s="4" r="M41">
+        <v>0</v>
+      </c>
+      <c s="4" r="N41">
+        <v>0</v>
+      </c>
+      <c s="4" r="O41">
+        <v>3960</v>
+      </c>
+      <c s="4" r="P41">
+        <v>196956</v>
+      </c>
+      <c s="4" r="Q41">
+        <v>0</v>
+      </c>
+      <c s="4" r="R41">
+        <v>66039.35</v>
+      </c>
+      <c s="4" r="S41">
+        <v>0</v>
+      </c>
+      <c s="4" r="T41">
+        <v>66039.35</v>
+      </c>
+      <c s="4" r="U41">
+        <v>130916.65</v>
+      </c>
+      <c s="4" r="V41">
+        <v>13091.67</v>
+      </c>
+      <c s="4" r="W41">
+        <v>144008.32</v>
+      </c>
+      <c s="5" t="str" r="X41"/>
+    </row>
+    <row r="42" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A42">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B42">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C42">
+        <is>
+          <t xml:space="preserve">5299770</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D42">
+        <is>
+          <t xml:space="preserve">TAHSİN MİRİOĞLU</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E42">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F42">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G42">
+        <is>
+          <t xml:space="preserve">11743</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H42">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1.5L 12X 70KCAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I42">
+        <is>
+          <t xml:space="preserve">126883</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J42">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K42">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L42">
+        <v>200</v>
+      </c>
+      <c s="4" r="M42">
+        <v>0</v>
+      </c>
+      <c s="4" r="N42">
+        <v>0</v>
+      </c>
+      <c s="4" r="O42">
+        <v>3859.92</v>
+      </c>
+      <c s="4" r="P42">
+        <v>141120</v>
+      </c>
+      <c s="4" r="Q42">
+        <v>0</v>
+      </c>
+      <c s="4" r="R42">
+        <v>35661.02</v>
+      </c>
+      <c s="4" r="S42">
+        <v>0</v>
+      </c>
+      <c s="4" r="T42">
+        <v>35661.02</v>
+      </c>
+      <c s="4" r="U42">
+        <v>105458.98</v>
+      </c>
+      <c s="4" r="V42">
+        <v>10545.90</v>
+      </c>
+      <c s="4" r="W42">
+        <v>116004.87</v>
+      </c>
+      <c s="5" t="str" r="X42"/>
+    </row>
+    <row r="43" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A43">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B43">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C43">
+        <is>
+          <t xml:space="preserve">5299770</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D43">
+        <is>
+          <t xml:space="preserve">TAHSİN MİRİOĞLU</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E43">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F43">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G43">
+        <is>
+          <t xml:space="preserve">11813</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H43">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I43">
+        <is>
+          <t xml:space="preserve">126883</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J43">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K43">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L43">
+        <v>400</v>
+      </c>
+      <c s="4" r="M43">
+        <v>0</v>
+      </c>
+      <c s="4" r="N43">
+        <v>0</v>
+      </c>
+      <c s="4" r="O43">
+        <v>5280</v>
+      </c>
+      <c s="4" r="P43">
+        <v>262608</v>
+      </c>
+      <c s="4" r="Q43">
+        <v>0</v>
+      </c>
+      <c s="4" r="R43">
+        <v>88052.46</v>
+      </c>
+      <c s="4" r="S43">
+        <v>0</v>
+      </c>
+      <c s="4" r="T43">
+        <v>88052.46</v>
+      </c>
+      <c s="4" r="U43">
+        <v>174555.54</v>
+      </c>
+      <c s="4" r="V43">
+        <v>17455.55</v>
+      </c>
+      <c s="4" r="W43">
+        <v>192011.09</v>
+      </c>
+      <c s="5" t="str" r="X43"/>
+    </row>
+    <row r="44" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A44">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B44">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C44">
+        <is>
+          <t xml:space="preserve">5306600</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D44">
+        <is>
+          <t xml:space="preserve">YENİ MİRİOĞLU GIDA MAD. SEBZE NAK.  SAN. TİC.LTD. ŞTİ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E44">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F44">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G44">
+        <is>
+          <t xml:space="preserve">11813</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H44">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I44">
+        <is>
+          <t xml:space="preserve">127041</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J44">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K44">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L44">
+        <v>400</v>
+      </c>
+      <c s="4" r="M44">
+        <v>0</v>
+      </c>
+      <c s="4" r="N44">
+        <v>0</v>
+      </c>
+      <c s="4" r="O44">
+        <v>5280</v>
+      </c>
+      <c s="4" r="P44">
+        <v>262608</v>
+      </c>
+      <c s="4" r="Q44">
+        <v>0</v>
+      </c>
+      <c s="4" r="R44">
+        <v>88052.46</v>
+      </c>
+      <c s="4" r="S44">
+        <v>0</v>
+      </c>
+      <c s="4" r="T44">
+        <v>88052.46</v>
+      </c>
+      <c s="4" r="U44">
+        <v>174555.54</v>
+      </c>
+      <c s="4" r="V44">
+        <v>17455.55</v>
+      </c>
+      <c s="4" r="W44">
+        <v>192011.09</v>
+      </c>
+      <c s="5" t="str" r="X44"/>
+    </row>
+    <row r="45" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A45">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B45">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C45">
+        <is>
+          <t xml:space="preserve">5483955</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D45">
+        <is>
+          <t xml:space="preserve">ÇOBANOĞLU TİCARET</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E45">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F45">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G45">
+        <is>
+          <t xml:space="preserve">11813</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H45">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I45">
+        <is>
+          <t xml:space="preserve">815696</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J45">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K45">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L45">
+        <v>250</v>
+      </c>
+      <c s="4" r="M45">
+        <v>0</v>
+      </c>
+      <c s="4" r="N45">
+        <v>0</v>
+      </c>
+      <c s="4" r="O45">
+        <v>3300</v>
+      </c>
+      <c s="4" r="P45">
+        <v>164130</v>
+      </c>
+      <c s="4" r="Q45">
+        <v>0</v>
+      </c>
+      <c s="4" r="R45">
+        <v>55032.79</v>
+      </c>
+      <c s="4" r="S45">
+        <v>0</v>
+      </c>
+      <c s="4" r="T45">
+        <v>55032.79</v>
+      </c>
+      <c s="4" r="U45">
+        <v>109097.21</v>
+      </c>
+      <c s="4" r="V45">
+        <v>10909.72</v>
+      </c>
+      <c s="4" r="W45">
+        <v>120006.93</v>
+      </c>
+      <c s="5" t="str" r="X45"/>
+    </row>
+    <row r="46" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A46">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B46">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C46">
+        <is>
+          <t xml:space="preserve">5483955</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D46">
+        <is>
+          <t xml:space="preserve">ÇOBANOĞLU TİCARET</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E46">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F46">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G46">
+        <is>
+          <t xml:space="preserve">11814</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H46">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL TURPAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I46">
+        <is>
+          <t xml:space="preserve">815696</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J46">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K46">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L46">
+        <v>450</v>
+      </c>
+      <c s="4" r="M46">
+        <v>0</v>
+      </c>
+      <c s="4" r="N46">
+        <v>0</v>
+      </c>
+      <c s="4" r="O46">
+        <v>5940</v>
+      </c>
+      <c s="4" r="P46">
+        <v>295434</v>
+      </c>
+      <c s="4" r="Q46">
+        <v>0</v>
+      </c>
+      <c s="4" r="R46">
+        <v>99059.02</v>
+      </c>
+      <c s="4" r="S46">
+        <v>0</v>
+      </c>
+      <c s="4" r="T46">
+        <v>99059.02</v>
+      </c>
+      <c s="4" r="U46">
+        <v>196374.98</v>
+      </c>
+      <c s="4" r="V46">
+        <v>19637.50</v>
+      </c>
+      <c s="4" r="W46">
+        <v>216012.48</v>
+      </c>
+      <c s="5" t="str" r="X46"/>
+    </row>
+    <row r="47" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A47">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B47">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C47">
+        <is>
+          <t xml:space="preserve">5483955</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D47">
+        <is>
+          <t xml:space="preserve">ÇOBANOĞLU TİCARET</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E47">
+        <is>
+          <t xml:space="preserve">28153</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F47">
+        <is>
+          <t xml:space="preserve">SELİMCAN TUNER</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G47">
+        <is>
+          <t xml:space="preserve">11859</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H47">
+        <is>
+          <t xml:space="preserve">PET YDG PRTKL 1L 12X LS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I47">
+        <is>
+          <t xml:space="preserve">815696</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J47">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K47">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L47">
+        <v>100</v>
+      </c>
+      <c s="4" r="M47">
+        <v>0</v>
+      </c>
+      <c s="4" r="N47">
+        <v>0</v>
+      </c>
+      <c s="4" r="O47">
+        <v>1310.04</v>
+      </c>
+      <c s="4" r="P47">
+        <v>65652</v>
+      </c>
+      <c s="4" r="Q47">
+        <v>0</v>
+      </c>
+      <c s="4" r="R47">
+        <v>22013.12</v>
+      </c>
+      <c s="4" r="S47">
+        <v>0</v>
+      </c>
+      <c s="4" r="T47">
+        <v>22013.12</v>
+      </c>
+      <c s="4" r="U47">
+        <v>43638.88</v>
+      </c>
+      <c s="4" r="V47">
+        <v>4363.89</v>
+      </c>
+      <c s="4" r="W47">
+        <v>48002.77</v>
+      </c>
+      <c s="5" t="str" r="X47"/>
+    </row>
+    <row r="48" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A48">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C48">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D48">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E48">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F48">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G48">
+        <is>
+          <t xml:space="preserve">11478</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H48">
+        <is>
+          <t xml:space="preserve">CAN 7UP GAZOZ 330ML 12X NO SUGAR SLEEK DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I48">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J48">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K48">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L48">
+        <v>4</v>
+      </c>
+      <c s="4" r="M48">
+        <v>0</v>
+      </c>
+      <c s="4" r="N48">
+        <v>0</v>
+      </c>
+      <c s="4" r="O48">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P48">
+        <v>2707.68</v>
+      </c>
+      <c s="4" r="Q48">
+        <v>0</v>
+      </c>
+      <c s="4" r="R48">
+        <v>1253.39</v>
+      </c>
+      <c s="4" r="S48">
+        <v>0</v>
+      </c>
+      <c s="4" r="T48">
+        <v>1253.39</v>
+      </c>
+      <c s="4" r="U48">
+        <v>1454.29</v>
+      </c>
+      <c s="4" r="V48">
+        <v>145.43</v>
+      </c>
+      <c s="4" r="W48">
+        <v>1599.72</v>
+      </c>
+      <c s="5" t="str" r="X48"/>
+    </row>
+    <row r="49" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A49">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B49">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C49">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D49">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E49">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F49">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G49">
+        <is>
+          <t xml:space="preserve">11683</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H49">
+        <is>
+          <t xml:space="preserve">CAN LIP AHU 330ML 12X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I49">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J49">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K49">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L49">
+        <v>4</v>
+      </c>
+      <c s="4" r="M49">
+        <v>0</v>
+      </c>
+      <c s="4" r="N49">
+        <v>0</v>
+      </c>
+      <c s="4" r="O49">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P49">
+        <v>2610.72</v>
+      </c>
+      <c s="4" r="Q49">
+        <v>0</v>
+      </c>
+      <c s="4" r="R49">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="S49">
+        <v>0</v>
+      </c>
+      <c s="4" r="T49">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="U49">
+        <v>1309.02</v>
+      </c>
+      <c s="4" r="V49">
+        <v>130.90</v>
+      </c>
+      <c s="4" r="W49">
+        <v>1439.92</v>
+      </c>
+      <c s="5" t="str" r="X49"/>
+    </row>
+    <row r="50" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A50">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C50">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D50">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E50">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F50">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G50">
+        <is>
+          <t xml:space="preserve">11441</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H50">
+        <is>
+          <t xml:space="preserve">CAN LIP KRP NANE 330ML 12X PROMO SLEEK DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I50">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J50">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K50">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L50">
+        <v>4</v>
+      </c>
+      <c s="4" r="M50">
+        <v>0</v>
+      </c>
+      <c s="4" r="N50">
+        <v>0</v>
+      </c>
+      <c s="4" r="O50">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P50">
+        <v>2610.72</v>
+      </c>
+      <c s="4" r="Q50">
+        <v>0</v>
+      </c>
+      <c s="4" r="R50">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="S50">
+        <v>0</v>
+      </c>
+      <c s="4" r="T50">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="U50">
+        <v>1309.02</v>
+      </c>
+      <c s="4" r="V50">
+        <v>130.90</v>
+      </c>
+      <c s="4" r="W50">
+        <v>1439.92</v>
+      </c>
+      <c s="5" t="str" r="X50"/>
+    </row>
+    <row r="51" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A51">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D51">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E51">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F51">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G51">
+        <is>
+          <t xml:space="preserve">11522</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H51">
+        <is>
+          <t xml:space="preserve">CAN LIP LIM 330ML 24X OP SLEEK NEW FP DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I51">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J51">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K51">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L51">
+        <v>2</v>
+      </c>
+      <c s="4" r="M51">
+        <v>0</v>
+      </c>
+      <c s="4" r="N51">
+        <v>0</v>
+      </c>
+      <c s="4" r="O51">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P51">
+        <v>2610.72</v>
+      </c>
+      <c s="4" r="Q51">
+        <v>0</v>
+      </c>
+      <c s="4" r="R51">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="S51">
+        <v>0</v>
+      </c>
+      <c s="4" r="T51">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="U51">
+        <v>1309.02</v>
+      </c>
+      <c s="4" r="V51">
+        <v>130.90</v>
+      </c>
+      <c s="4" r="W51">
+        <v>1439.92</v>
+      </c>
+      <c s="5" t="str" r="X51"/>
+    </row>
+    <row r="52" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A52">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D52">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E52">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F52">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G52">
+        <is>
+          <t xml:space="preserve">11658</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H52">
+        <is>
+          <t xml:space="preserve">CAN LIP MANGO 330ML 12X SLEEK DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I52">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J52">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K52">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L52">
+        <v>4</v>
+      </c>
+      <c s="4" r="M52">
+        <v>0</v>
+      </c>
+      <c s="4" r="N52">
+        <v>0</v>
+      </c>
+      <c s="4" r="O52">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P52">
+        <v>2610.72</v>
+      </c>
+      <c s="4" r="Q52">
+        <v>0</v>
+      </c>
+      <c s="4" r="R52">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="S52">
+        <v>0</v>
+      </c>
+      <c s="4" r="T52">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="U52">
+        <v>1309.02</v>
+      </c>
+      <c s="4" r="V52">
+        <v>130.90</v>
+      </c>
+      <c s="4" r="W52">
+        <v>1439.92</v>
+      </c>
+      <c s="5" t="str" r="X52"/>
+    </row>
+    <row r="53" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A53">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D53">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E53">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F53">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G53">
+        <is>
+          <t xml:space="preserve">11944</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H53">
+        <is>
+          <t xml:space="preserve">CAN LIP MANGO 500ML 12X FE 2026</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I53">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J53">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K53">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L53">
+        <v>5</v>
+      </c>
+      <c s="4" r="M53">
+        <v>0</v>
+      </c>
+      <c s="4" r="N53">
+        <v>0</v>
+      </c>
+      <c s="4" r="O53">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P53">
+        <v>3263.40</v>
+      </c>
+      <c s="4" r="Q53">
+        <v>0</v>
+      </c>
+      <c s="4" r="R53">
+        <v>1445.36</v>
+      </c>
+      <c s="4" r="S53">
+        <v>0</v>
+      </c>
+      <c s="4" r="T53">
+        <v>1445.36</v>
+      </c>
+      <c s="4" r="U53">
+        <v>1818.04</v>
+      </c>
+      <c s="4" r="V53">
+        <v>181.80</v>
+      </c>
+      <c s="4" r="W53">
+        <v>1999.84</v>
+      </c>
+      <c s="5" t="str" r="X53"/>
+    </row>
+    <row r="54" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A54">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D54">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E54">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F54">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G54">
+        <is>
+          <t xml:space="preserve">11873</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H54">
+        <is>
+          <t xml:space="preserve">CAN LIP PRTK&amp;MAN 330ML 12X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I54">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J54">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K54">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L54">
+        <v>4</v>
+      </c>
+      <c s="4" r="M54">
+        <v>0</v>
+      </c>
+      <c s="4" r="N54">
+        <v>0</v>
+      </c>
+      <c s="4" r="O54">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P54">
+        <v>2610.72</v>
+      </c>
+      <c s="4" r="Q54">
+        <v>0</v>
+      </c>
+      <c s="4" r="R54">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="S54">
+        <v>0</v>
+      </c>
+      <c s="4" r="T54">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="U54">
+        <v>1309.02</v>
+      </c>
+      <c s="4" r="V54">
+        <v>130.90</v>
+      </c>
+      <c s="4" r="W54">
+        <v>1439.92</v>
+      </c>
+      <c s="5" t="str" r="X54"/>
+    </row>
+    <row r="55" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A55">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D55">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E55">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F55">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G55">
+        <is>
+          <t xml:space="preserve">11531</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H55">
+        <is>
+          <t xml:space="preserve">CAN LIP SEFT 330ML 24X OP SLEEK DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I55">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J55">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K55">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L55">
+        <v>2</v>
+      </c>
+      <c s="4" r="M55">
+        <v>0</v>
+      </c>
+      <c s="4" r="N55">
+        <v>0</v>
+      </c>
+      <c s="4" r="O55">
+        <v>16.86</v>
+      </c>
+      <c s="4" r="P55">
+        <v>2610.72</v>
+      </c>
+      <c s="4" r="Q55">
+        <v>0</v>
+      </c>
+      <c s="4" r="R55">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="S55">
+        <v>0</v>
+      </c>
+      <c s="4" r="T55">
+        <v>1301.70</v>
+      </c>
+      <c s="4" r="U55">
+        <v>1309.02</v>
+      </c>
+      <c s="4" r="V55">
+        <v>130.90</v>
+      </c>
+      <c s="4" r="W55">
+        <v>1439.92</v>
+      </c>
+      <c s="5" t="str" r="X55"/>
+    </row>
+    <row r="56" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A56">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D56">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E56">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F56">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G56">
+        <is>
+          <t xml:space="preserve">11943</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H56">
+        <is>
+          <t xml:space="preserve">CAN LIP SEFT 500ML 12X FE 2026</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I56">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J56">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K56">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L56">
+        <v>5</v>
+      </c>
+      <c s="4" r="M56">
+        <v>0</v>
+      </c>
+      <c s="4" r="N56">
+        <v>0</v>
+      </c>
+      <c s="4" r="O56">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P56">
+        <v>3263.40</v>
+      </c>
+      <c s="4" r="Q56">
+        <v>0</v>
+      </c>
+      <c s="4" r="R56">
+        <v>1445.36</v>
+      </c>
+      <c s="4" r="S56">
+        <v>0</v>
+      </c>
+      <c s="4" r="T56">
+        <v>1445.36</v>
+      </c>
+      <c s="4" r="U56">
+        <v>1818.04</v>
+      </c>
+      <c s="4" r="V56">
+        <v>181.80</v>
+      </c>
+      <c s="4" r="W56">
+        <v>1999.84</v>
+      </c>
+      <c s="5" t="str" r="X56"/>
+    </row>
+    <row r="57" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A57">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D57">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E57">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F57">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G57">
+        <is>
+          <t xml:space="preserve">11527</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H57">
+        <is>
+          <t xml:space="preserve">CAN PC KOLA 330ML 24X OP SLEEK 100KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I57">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J57">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K57">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L57">
+        <v>3</v>
+      </c>
+      <c s="4" r="M57">
+        <v>0</v>
+      </c>
+      <c s="4" r="N57">
+        <v>0</v>
+      </c>
+      <c s="4" r="O57">
+        <v>25.73</v>
+      </c>
+      <c s="4" r="P57">
+        <v>4061.52</v>
+      </c>
+      <c s="4" r="Q57">
+        <v>0</v>
+      </c>
+      <c s="4" r="R57">
+        <v>1573.21</v>
+      </c>
+      <c s="4" r="S57">
+        <v>0</v>
+      </c>
+      <c s="4" r="T57">
+        <v>1573.21</v>
+      </c>
+      <c s="4" r="U57">
+        <v>2488.31</v>
+      </c>
+      <c s="4" r="V57">
+        <v>248.83</v>
+      </c>
+      <c s="4" r="W57">
+        <v>2737.14</v>
+      </c>
+      <c s="5" t="str" r="X57"/>
+    </row>
+    <row r="58" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A58">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D58">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E58">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F58">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G58">
+        <is>
+          <t xml:space="preserve">11464</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H58">
+        <is>
+          <t xml:space="preserve">CAN PC MAX KOLA 330ML 12X SLEEK DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I58">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J58">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K58">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L58">
+        <v>4</v>
+      </c>
+      <c s="4" r="M58">
+        <v>0</v>
+      </c>
+      <c s="4" r="N58">
+        <v>0</v>
+      </c>
+      <c s="4" r="O58">
+        <v>17.05</v>
+      </c>
+      <c s="4" r="P58">
+        <v>2707.68</v>
+      </c>
+      <c s="4" r="Q58">
+        <v>0</v>
+      </c>
+      <c s="4" r="R58">
+        <v>1048.81</v>
+      </c>
+      <c s="4" r="S58">
+        <v>0</v>
+      </c>
+      <c s="4" r="T58">
+        <v>1048.81</v>
+      </c>
+      <c s="4" r="U58">
+        <v>1658.87</v>
+      </c>
+      <c s="4" r="V58">
+        <v>165.89</v>
+      </c>
+      <c s="4" r="W58">
+        <v>1824.76</v>
+      </c>
+      <c s="5" t="str" r="X58"/>
+    </row>
+    <row r="59" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A59">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D59">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E59">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F59">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G59">
+        <is>
+          <t xml:space="preserve">11170</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H59">
+        <is>
+          <t xml:space="preserve">CAN TRPCN MIX 330ML 12X 25% JUICE DRINK SLEEK</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I59">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J59">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K59">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L59">
+        <v>2</v>
+      </c>
+      <c s="4" r="M59">
+        <v>0</v>
+      </c>
+      <c s="4" r="N59">
+        <v>0</v>
+      </c>
+      <c s="4" r="O59">
+        <v>8.57</v>
+      </c>
+      <c s="4" r="P59">
+        <v>1353.84</v>
+      </c>
+      <c s="4" r="Q59">
+        <v>0</v>
+      </c>
+      <c s="4" r="R59">
+        <v>626.69</v>
+      </c>
+      <c s="4" r="S59">
+        <v>0</v>
+      </c>
+      <c s="4" r="T59">
+        <v>626.69</v>
+      </c>
+      <c s="4" r="U59">
+        <v>727.15</v>
+      </c>
+      <c s="4" r="V59">
+        <v>72.71</v>
+      </c>
+      <c s="4" r="W59">
+        <v>799.86</v>
+      </c>
+      <c s="5" t="str" r="X59"/>
+    </row>
+    <row r="60" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A60">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D60">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E60">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F60">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G60">
+        <is>
+          <t xml:space="preserve">11172</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H60">
+        <is>
+          <t xml:space="preserve">CAN TRPCN SEFT 330ML 12X BURSA 25% JUICE DRINK SLEEK</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I60">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J60">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K60">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L60">
+        <v>2</v>
+      </c>
+      <c s="4" r="M60">
+        <v>0</v>
+      </c>
+      <c s="4" r="N60">
+        <v>0</v>
+      </c>
+      <c s="4" r="O60">
+        <v>8.43</v>
+      </c>
+      <c s="4" r="P60">
+        <v>1353.84</v>
+      </c>
+      <c s="4" r="Q60">
+        <v>0</v>
+      </c>
+      <c s="4" r="R60">
+        <v>626.69</v>
+      </c>
+      <c s="4" r="S60">
+        <v>0</v>
+      </c>
+      <c s="4" r="T60">
+        <v>626.69</v>
+      </c>
+      <c s="4" r="U60">
+        <v>727.15</v>
+      </c>
+      <c s="4" r="V60">
+        <v>72.71</v>
+      </c>
+      <c s="4" r="W60">
+        <v>799.86</v>
+      </c>
+      <c s="5" t="str" r="X60"/>
+    </row>
+    <row r="61" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A61">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D61">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E61">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F61">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G61">
+        <is>
+          <t xml:space="preserve">11173</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H61">
+        <is>
+          <t xml:space="preserve">CAN TRPCN VISNE 330ML 12X AFYON 25% JUICE DRINK SLEEK</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I61">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J61">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K61">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L61">
+        <v>2</v>
+      </c>
+      <c s="4" r="M61">
+        <v>0</v>
+      </c>
+      <c s="4" r="N61">
+        <v>0</v>
+      </c>
+      <c s="4" r="O61">
+        <v>8.69</v>
+      </c>
+      <c s="4" r="P61">
+        <v>1353.84</v>
+      </c>
+      <c s="4" r="Q61">
+        <v>0</v>
+      </c>
+      <c s="4" r="R61">
+        <v>626.69</v>
+      </c>
+      <c s="4" r="S61">
+        <v>0</v>
+      </c>
+      <c s="4" r="T61">
+        <v>626.69</v>
+      </c>
+      <c s="4" r="U61">
+        <v>727.15</v>
+      </c>
+      <c s="4" r="V61">
+        <v>72.71</v>
+      </c>
+      <c s="4" r="W61">
+        <v>799.86</v>
+      </c>
+      <c s="5" t="str" r="X61"/>
+    </row>
+    <row r="62" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A62">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C62">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D62">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E62">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F62">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G62">
+        <is>
+          <t xml:space="preserve">11857</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H62">
+        <is>
+          <t xml:space="preserve">CAN YDG PRTKL 330ML 12X LS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I62">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J62">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K62">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L62">
+        <v>2</v>
+      </c>
+      <c s="4" r="M62">
+        <v>0</v>
+      </c>
+      <c s="4" r="N62">
+        <v>0</v>
+      </c>
+      <c s="4" r="O62">
+        <v>8.43</v>
+      </c>
+      <c s="4" r="P62">
+        <v>1353.84</v>
+      </c>
+      <c s="4" r="Q62">
+        <v>0</v>
+      </c>
+      <c s="4" r="R62">
+        <v>524.40</v>
+      </c>
+      <c s="4" r="S62">
+        <v>0</v>
+      </c>
+      <c s="4" r="T62">
+        <v>524.40</v>
+      </c>
+      <c s="4" r="U62">
+        <v>829.44</v>
+      </c>
+      <c s="4" r="V62">
+        <v>82.94</v>
+      </c>
+      <c s="4" r="W62">
+        <v>912.38</v>
+      </c>
+      <c s="5" t="str" r="X62"/>
+    </row>
+    <row r="63" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A63">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D63">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E63">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F63">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G63">
+        <is>
+          <t xml:space="preserve">11454</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H63">
+        <is>
+          <t xml:space="preserve">NRB PC KOLA 200ML 24X 100KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I63">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J63">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K63">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L63">
+        <v>3</v>
+      </c>
+      <c s="4" r="M63">
+        <v>0</v>
+      </c>
+      <c s="4" r="N63">
+        <v>0</v>
+      </c>
+      <c s="4" r="O63">
+        <v>18.96</v>
+      </c>
+      <c s="4" r="P63">
+        <v>2052.72</v>
+      </c>
+      <c s="4" r="Q63">
+        <v>0</v>
+      </c>
+      <c s="4" r="R63">
+        <v>560.91</v>
+      </c>
+      <c s="4" r="S63">
+        <v>0</v>
+      </c>
+      <c s="4" r="T63">
+        <v>560.91</v>
+      </c>
+      <c s="4" r="U63">
+        <v>1491.81</v>
+      </c>
+      <c s="4" r="V63">
+        <v>149.18</v>
+      </c>
+      <c s="4" r="W63">
+        <v>1641.00</v>
+      </c>
+      <c s="5" t="str" r="X63"/>
+    </row>
+    <row r="64" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A64">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C64">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D64">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E64">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F64">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G64">
+        <is>
+          <t xml:space="preserve">11446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H64">
+        <is>
+          <t xml:space="preserve">PET FRK GAZOZ 1.5L 12X 20KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I64">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J64">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K64">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L64">
+        <v>2</v>
+      </c>
+      <c s="4" r="M64">
+        <v>0</v>
+      </c>
+      <c s="4" r="N64">
+        <v>0</v>
+      </c>
+      <c s="4" r="O64">
+        <v>37.86</v>
+      </c>
+      <c s="4" r="P64">
+        <v>1441.44</v>
+      </c>
+      <c s="4" r="Q64">
+        <v>0</v>
+      </c>
+      <c s="4" r="R64">
+        <v>378.48</v>
+      </c>
+      <c s="4" r="S64">
+        <v>0</v>
+      </c>
+      <c s="4" r="T64">
+        <v>378.48</v>
+      </c>
+      <c s="4" r="U64">
+        <v>1062.96</v>
+      </c>
+      <c s="4" r="V64">
+        <v>106.30</v>
+      </c>
+      <c s="4" r="W64">
+        <v>1169.26</v>
+      </c>
+      <c s="5" t="str" r="X64"/>
+    </row>
+    <row r="65" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A65">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B65">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C65">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D65">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E65">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F65">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G65">
+        <is>
+          <t xml:space="preserve">11543</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H65">
+        <is>
+          <t xml:space="preserve">PET FRK GAZOZ 2.5L 6X 20KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I65">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J65">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K65">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L65">
+        <v>5</v>
+      </c>
+      <c s="4" r="M65">
+        <v>0</v>
+      </c>
+      <c s="4" r="N65">
+        <v>0</v>
+      </c>
+      <c s="4" r="O65">
+        <v>79.00</v>
+      </c>
+      <c s="4" r="P65">
+        <v>2070</v>
+      </c>
+      <c s="4" r="Q65">
+        <v>0</v>
+      </c>
+      <c s="4" r="R65">
+        <v>605.70</v>
+      </c>
+      <c s="4" r="S65">
+        <v>0</v>
+      </c>
+      <c s="4" r="T65">
+        <v>605.70</v>
+      </c>
+      <c s="4" r="U65">
+        <v>1464.30</v>
+      </c>
+      <c s="4" r="V65">
+        <v>146.43</v>
+      </c>
+      <c s="4" r="W65">
+        <v>1610.73</v>
+      </c>
+      <c s="5" t="str" r="X65"/>
+    </row>
+    <row r="66" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A66">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D66">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E66">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F66">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G66">
+        <is>
+          <t xml:space="preserve">11685</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H66">
+        <is>
+          <t xml:space="preserve">PET LIP AHU 1L 6X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I66">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J66">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K66">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L66">
+        <v>3</v>
+      </c>
+      <c s="4" r="M66">
+        <v>0</v>
+      </c>
+      <c s="4" r="N66">
+        <v>0</v>
+      </c>
+      <c s="4" r="O66">
+        <v>19.50</v>
+      </c>
+      <c s="4" r="P66">
+        <v>990</v>
+      </c>
+      <c s="4" r="Q66">
+        <v>0</v>
+      </c>
+      <c s="4" r="R66">
+        <v>308.09</v>
+      </c>
+      <c s="4" r="S66">
+        <v>0</v>
+      </c>
+      <c s="4" r="T66">
+        <v>308.09</v>
+      </c>
+      <c s="4" r="U66">
+        <v>681.91</v>
+      </c>
+      <c s="4" r="V66">
+        <v>68.19</v>
+      </c>
+      <c s="4" r="W66">
+        <v>750.10</v>
+      </c>
+      <c s="5" t="str" r="X66"/>
+    </row>
+    <row r="67" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A67">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D67">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E67">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F67">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G67">
+        <is>
+          <t xml:space="preserve">11822</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H67">
+        <is>
+          <t xml:space="preserve">PET LIP KRP NANE 1.5L 6X SIRENADRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I67">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J67">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K67">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L67">
+        <v>2</v>
+      </c>
+      <c s="4" r="M67">
+        <v>0</v>
+      </c>
+      <c s="4" r="N67">
+        <v>0</v>
+      </c>
+      <c s="4" r="O67">
+        <v>19.00</v>
+      </c>
+      <c s="4" r="P67">
+        <v>753.12</v>
+      </c>
+      <c s="4" r="Q67">
+        <v>0</v>
+      </c>
+      <c s="4" r="R67">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="S67">
+        <v>0</v>
+      </c>
+      <c s="4" r="T67">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="U67">
+        <v>526.88</v>
+      </c>
+      <c s="4" r="V67">
+        <v>52.69</v>
+      </c>
+      <c s="4" r="W67">
+        <v>579.57</v>
+      </c>
+      <c s="5" t="str" r="X67"/>
+    </row>
+    <row r="68" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A68">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D68">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E68">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F68">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G68">
+        <is>
+          <t xml:space="preserve">11490</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H68">
+        <is>
+          <t xml:space="preserve">PET LIP KRP NANE 1L 6X SIRENA NEW DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I68">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J68">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K68">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L68">
+        <v>5</v>
+      </c>
+      <c s="4" r="M68">
+        <v>0</v>
+      </c>
+      <c s="4" r="N68">
+        <v>0</v>
+      </c>
+      <c s="4" r="O68">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P68">
+        <v>1650</v>
+      </c>
+      <c s="4" r="Q68">
+        <v>0</v>
+      </c>
+      <c s="4" r="R68">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="S68">
+        <v>0</v>
+      </c>
+      <c s="4" r="T68">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="U68">
+        <v>1136.52</v>
+      </c>
+      <c s="4" r="V68">
+        <v>113.65</v>
+      </c>
+      <c s="4" r="W68">
+        <v>1250.17</v>
+      </c>
+      <c s="5" t="str" r="X68"/>
+    </row>
+    <row r="69" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A69">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D69">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E69">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F69">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G69">
+        <is>
+          <t xml:space="preserve">11823</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H69">
+        <is>
+          <t xml:space="preserve">PET LIP LIM 1.5L 6X SIRENA NEWFP DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I69">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J69">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K69">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L69">
+        <v>2</v>
+      </c>
+      <c s="4" r="M69">
+        <v>0</v>
+      </c>
+      <c s="4" r="N69">
+        <v>0</v>
+      </c>
+      <c s="4" r="O69">
+        <v>19.00</v>
+      </c>
+      <c s="4" r="P69">
+        <v>753.12</v>
+      </c>
+      <c s="4" r="Q69">
+        <v>0</v>
+      </c>
+      <c s="4" r="R69">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="S69">
+        <v>0</v>
+      </c>
+      <c s="4" r="T69">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="U69">
+        <v>526.88</v>
+      </c>
+      <c s="4" r="V69">
+        <v>52.69</v>
+      </c>
+      <c s="4" r="W69">
+        <v>579.57</v>
+      </c>
+      <c s="5" t="str" r="X69"/>
+    </row>
+    <row r="70" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A70">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D70">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E70">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F70">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G70">
+        <is>
+          <t xml:space="preserve">11486</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H70">
+        <is>
+          <t xml:space="preserve">PET LIP LIM 1L 6X SIRENA NEW FP DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I70">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J70">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K70">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L70">
+        <v>5</v>
+      </c>
+      <c s="4" r="M70">
+        <v>0</v>
+      </c>
+      <c s="4" r="N70">
+        <v>0</v>
+      </c>
+      <c s="4" r="O70">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P70">
+        <v>1650</v>
+      </c>
+      <c s="4" r="Q70">
+        <v>0</v>
+      </c>
+      <c s="4" r="R70">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="S70">
+        <v>0</v>
+      </c>
+      <c s="4" r="T70">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="U70">
+        <v>1136.52</v>
+      </c>
+      <c s="4" r="V70">
+        <v>113.65</v>
+      </c>
+      <c s="4" r="W70">
+        <v>1250.17</v>
+      </c>
+      <c s="5" t="str" r="X70"/>
+    </row>
+    <row r="71" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A71">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D71">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E71">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F71">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G71">
+        <is>
+          <t xml:space="preserve">11824</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H71">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1.5L 6X SIRENADRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I71">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J71">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K71">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L71">
+        <v>2</v>
+      </c>
+      <c s="4" r="M71">
+        <v>0</v>
+      </c>
+      <c s="4" r="N71">
+        <v>0</v>
+      </c>
+      <c s="4" r="O71">
+        <v>19.00</v>
+      </c>
+      <c s="4" r="P71">
+        <v>753.12</v>
+      </c>
+      <c s="4" r="Q71">
+        <v>0</v>
+      </c>
+      <c s="4" r="R71">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="S71">
+        <v>0</v>
+      </c>
+      <c s="4" r="T71">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="U71">
+        <v>526.88</v>
+      </c>
+      <c s="4" r="V71">
+        <v>52.69</v>
+      </c>
+      <c s="4" r="W71">
+        <v>579.57</v>
+      </c>
+      <c s="5" t="str" r="X71"/>
+    </row>
+    <row r="72" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A72">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D72">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E72">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F72">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G72">
+        <is>
+          <t xml:space="preserve">11488</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H72">
+        <is>
+          <t xml:space="preserve">PET LIP MANGO 1L 6X DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I72">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J72">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K72">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L72">
+        <v>5</v>
+      </c>
+      <c s="4" r="M72">
+        <v>0</v>
+      </c>
+      <c s="4" r="N72">
+        <v>0</v>
+      </c>
+      <c s="4" r="O72">
+        <v>32.00</v>
+      </c>
+      <c s="4" r="P72">
+        <v>1650</v>
+      </c>
+      <c s="4" r="Q72">
+        <v>0</v>
+      </c>
+      <c s="4" r="R72">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="S72">
+        <v>0</v>
+      </c>
+      <c s="4" r="T72">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="U72">
+        <v>1136.52</v>
+      </c>
+      <c s="4" r="V72">
+        <v>113.65</v>
+      </c>
+      <c s="4" r="W72">
+        <v>1250.17</v>
+      </c>
+      <c s="5" t="str" r="X72"/>
+    </row>
+    <row r="73" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A73">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D73">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E73">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F73">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G73">
+        <is>
+          <t xml:space="preserve">11874</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H73">
+        <is>
+          <t xml:space="preserve">PET LIP PRTK&amp;MAN 1L 6X</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I73">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J73">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K73">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L73">
+        <v>5</v>
+      </c>
+      <c s="4" r="M73">
+        <v>0</v>
+      </c>
+      <c s="4" r="N73">
+        <v>0</v>
+      </c>
+      <c s="4" r="O73">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P73">
+        <v>1650</v>
+      </c>
+      <c s="4" r="Q73">
+        <v>0</v>
+      </c>
+      <c s="4" r="R73">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="S73">
+        <v>0</v>
+      </c>
+      <c s="4" r="T73">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="U73">
+        <v>1136.52</v>
+      </c>
+      <c s="4" r="V73">
+        <v>113.65</v>
+      </c>
+      <c s="4" r="W73">
+        <v>1250.17</v>
+      </c>
+      <c s="5" t="str" r="X73"/>
+    </row>
+    <row r="74" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A74">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D74">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E74">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F74">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G74">
+        <is>
+          <t xml:space="preserve">11675</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H74">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1.5L 6X ROMANYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I74">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J74">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K74">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L74">
+        <v>2</v>
+      </c>
+      <c s="4" r="M74">
+        <v>0</v>
+      </c>
+      <c s="4" r="N74">
+        <v>0</v>
+      </c>
+      <c s="4" r="O74">
+        <v>18.82</v>
+      </c>
+      <c s="4" r="P74">
+        <v>753.12</v>
+      </c>
+      <c s="4" r="Q74">
+        <v>0</v>
+      </c>
+      <c s="4" r="R74">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="S74">
+        <v>0</v>
+      </c>
+      <c s="4" r="T74">
+        <v>226.24</v>
+      </c>
+      <c s="4" r="U74">
+        <v>526.88</v>
+      </c>
+      <c s="4" r="V74">
+        <v>52.69</v>
+      </c>
+      <c s="4" r="W74">
+        <v>579.57</v>
+      </c>
+      <c s="5" t="str" r="X74"/>
+    </row>
+    <row r="75" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A75">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D75">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E75">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F75">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G75">
+        <is>
+          <t xml:space="preserve">11515</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H75">
+        <is>
+          <t xml:space="preserve">PET LIP SEFT 1L 6X SIRENA DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I75">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J75">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K75">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L75">
+        <v>5</v>
+      </c>
+      <c s="4" r="M75">
+        <v>0</v>
+      </c>
+      <c s="4" r="N75">
+        <v>0</v>
+      </c>
+      <c s="4" r="O75">
+        <v>32.50</v>
+      </c>
+      <c s="4" r="P75">
+        <v>1650</v>
+      </c>
+      <c s="4" r="Q75">
+        <v>0</v>
+      </c>
+      <c s="4" r="R75">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="S75">
+        <v>0</v>
+      </c>
+      <c s="4" r="T75">
+        <v>513.48</v>
+      </c>
+      <c s="4" r="U75">
+        <v>1136.52</v>
+      </c>
+      <c s="4" r="V75">
+        <v>113.65</v>
+      </c>
+      <c s="4" r="W75">
+        <v>1250.17</v>
+      </c>
+      <c s="5" t="str" r="X75"/>
+    </row>
+    <row r="76" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A76">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D76">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E76">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F76">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G76">
+        <is>
+          <t xml:space="preserve">11743</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H76">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1.5L 12X 70KCAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I76">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J76">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K76">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L76">
+        <v>5</v>
+      </c>
+      <c s="4" r="M76">
+        <v>0</v>
+      </c>
+      <c s="4" r="N76">
+        <v>0</v>
+      </c>
+      <c s="4" r="O76">
+        <v>96.50</v>
+      </c>
+      <c s="4" r="P76">
+        <v>3528</v>
+      </c>
+      <c s="4" r="Q76">
+        <v>0</v>
+      </c>
+      <c s="4" r="R76">
+        <v>646.76</v>
+      </c>
+      <c s="4" r="S76">
+        <v>0</v>
+      </c>
+      <c s="4" r="T76">
+        <v>646.76</v>
+      </c>
+      <c s="4" r="U76">
+        <v>2881.24</v>
+      </c>
+      <c s="4" r="V76">
+        <v>288.12</v>
+      </c>
+      <c s="4" r="W76">
+        <v>3169.37</v>
+      </c>
+      <c s="5" t="str" r="X76"/>
+    </row>
+    <row r="77" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A77">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D77">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E77">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F77">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G77">
+        <is>
+          <t xml:space="preserve">11813</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H77">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 1L 12X 70KCAL</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I77">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J77">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K77">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L77">
+        <v>6</v>
+      </c>
+      <c s="4" r="M77">
+        <v>0</v>
+      </c>
+      <c s="4" r="N77">
+        <v>0</v>
+      </c>
+      <c s="4" r="O77">
+        <v>79.20</v>
+      </c>
+      <c s="4" r="P77">
+        <v>3939.12</v>
+      </c>
+      <c s="4" r="Q77">
+        <v>0</v>
+      </c>
+      <c s="4" r="R77">
+        <v>993.84</v>
+      </c>
+      <c s="4" r="S77">
+        <v>0</v>
+      </c>
+      <c s="4" r="T77">
+        <v>993.84</v>
+      </c>
+      <c s="4" r="U77">
+        <v>2945.28</v>
+      </c>
+      <c s="4" r="V77">
+        <v>294.53</v>
+      </c>
+      <c s="4" r="W77">
+        <v>3239.81</v>
+      </c>
+      <c s="5" t="str" r="X77"/>
+    </row>
+    <row r="78" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A78">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D78">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E78">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F78">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G78">
+        <is>
+          <t xml:space="preserve">11452</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H78">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 2.5L 6X 100KCAL DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I78">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J78">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K78">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L78">
+        <v>14</v>
+      </c>
+      <c s="4" r="M78">
+        <v>0</v>
+      </c>
+      <c s="4" r="N78">
+        <v>0</v>
+      </c>
+      <c s="4" r="O78">
+        <v>224.00</v>
+      </c>
+      <c s="4" r="P78">
+        <v>6845.16</v>
+      </c>
+      <c s="4" r="Q78">
+        <v>0</v>
+      </c>
+      <c s="4" r="R78">
+        <v>1758.59</v>
+      </c>
+      <c s="4" r="S78">
+        <v>0</v>
+      </c>
+      <c s="4" r="T78">
+        <v>1758.59</v>
+      </c>
+      <c s="4" r="U78">
+        <v>5086.57</v>
+      </c>
+      <c s="4" r="V78">
+        <v>508.66</v>
+      </c>
+      <c s="4" r="W78">
+        <v>5595.23</v>
+      </c>
+      <c s="5" t="str" r="X78"/>
+    </row>
+    <row r="79" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A79">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D79">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E79">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F79">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G79">
+        <is>
+          <t xml:space="preserve">11930</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H79">
+        <is>
+          <t xml:space="preserve">PET PC KOLA 2L 6X 70KCAL FE 2026</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I79">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J79">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K79">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L79">
+        <v>5</v>
+      </c>
+      <c s="4" r="M79">
+        <v>0</v>
+      </c>
+      <c s="4" r="N79">
+        <v>0</v>
+      </c>
+      <c s="4" r="O79">
+        <v>65.00</v>
+      </c>
+      <c s="4" r="P79">
+        <v>1701.30</v>
+      </c>
+      <c s="4" r="Q79">
+        <v>0</v>
+      </c>
+      <c s="4" r="R79">
+        <v>258.26</v>
+      </c>
+      <c s="4" r="S79">
+        <v>0</v>
+      </c>
+      <c s="4" r="T79">
+        <v>258.26</v>
+      </c>
+      <c s="4" r="U79">
+        <v>1443.04</v>
+      </c>
+      <c s="4" r="V79">
+        <v>144.30</v>
+      </c>
+      <c s="4" r="W79">
+        <v>1587.35</v>
+      </c>
+      <c s="5" t="str" r="X79"/>
+    </row>
+    <row r="80" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A80">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D80">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E80">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F80">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G80">
+        <is>
+          <t xml:space="preserve">11451</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H80">
+        <is>
+          <t xml:space="preserve">PET PC MAX KOLA 1L 12X DRS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I80">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J80">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K80">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L80">
+        <v>3</v>
+      </c>
+      <c s="4" r="M80">
+        <v>0</v>
+      </c>
+      <c s="4" r="N80">
+        <v>0</v>
+      </c>
+      <c s="4" r="O80">
+        <v>38.10</v>
+      </c>
+      <c s="4" r="P80">
+        <v>1969.56</v>
+      </c>
+      <c s="4" r="Q80">
+        <v>0</v>
+      </c>
+      <c s="4" r="R80">
+        <v>496.92</v>
+      </c>
+      <c s="4" r="S80">
+        <v>0</v>
+      </c>
+      <c s="4" r="T80">
+        <v>496.92</v>
+      </c>
+      <c s="4" r="U80">
+        <v>1472.64</v>
+      </c>
+      <c s="4" r="V80">
+        <v>147.26</v>
+      </c>
+      <c s="4" r="W80">
+        <v>1619.90</v>
+      </c>
+      <c s="5" t="str" r="X80"/>
+    </row>
+    <row r="81" ht="17.05" customHeight="0">
+      <c s="3" t="inlineStr" r="A81">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B81">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D81">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E81">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F81">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G81">
+        <is>
+          <t xml:space="preserve">11860</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H81">
+        <is>
+          <t xml:space="preserve">PET YDG PRTKL 1.5L 12X LS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I81">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J81">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K81">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L81">
+        <v>5</v>
+      </c>
+      <c s="4" r="M81">
+        <v>0</v>
+      </c>
+      <c s="4" r="N81">
+        <v>0</v>
+      </c>
+      <c s="4" r="O81">
+        <v>95.25</v>
+      </c>
+      <c s="4" r="P81">
+        <v>3528</v>
+      </c>
+      <c s="4" r="Q81">
+        <v>0</v>
+      </c>
+      <c s="4" r="R81">
+        <v>646.76</v>
+      </c>
+      <c s="4" r="S81">
+        <v>0</v>
+      </c>
+      <c s="4" r="T81">
+        <v>646.76</v>
+      </c>
+      <c s="4" r="U81">
+        <v>2881.24</v>
+      </c>
+      <c s="4" r="V81">
+        <v>288.12</v>
+      </c>
+      <c s="4" r="W81">
+        <v>3169.37</v>
+      </c>
+      <c s="5" t="str" r="X81"/>
+    </row>
+    <row r="82" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A82">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C82">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D82">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E82">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F82">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G82">
+        <is>
+          <t xml:space="preserve">11859</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="H82">
+        <is>
+          <t xml:space="preserve">PET YDG PRTKL 1L 12X LS</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="I82">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J82">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K82">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L82">
+        <v>6</v>
+      </c>
+      <c s="4" r="M82">
+        <v>0</v>
+      </c>
+      <c s="4" r="N82">
+        <v>0</v>
+      </c>
+      <c s="4" r="O82">
+        <v>78.60</v>
+      </c>
+      <c s="4" r="P82">
+        <v>3939.12</v>
+      </c>
+      <c s="4" r="Q82">
+        <v>0</v>
+      </c>
+      <c s="4" r="R82">
+        <v>993.84</v>
+      </c>
+      <c s="4" r="S82">
+        <v>0</v>
+      </c>
+      <c s="4" r="T82">
+        <v>993.84</v>
+      </c>
+      <c s="4" r="U82">
+        <v>2945.28</v>
+      </c>
+      <c s="4" r="V82">
+        <v>294.53</v>
+      </c>
+      <c s="4" r="W82">
+        <v>3239.81</v>
+      </c>
+      <c s="5" t="str" r="X82"/>
+    </row>
+    <row r="83" ht="17" customHeight="0">
+      <c s="3" t="inlineStr" r="A83">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">BEV-ANTAKYA</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">6161438</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="D83">
+        <is>
+          <t xml:space="preserve">ŞABANOĞLU GRUP GIDA VE TİCARET AŞ.</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="E83">
+        <is>
+          <t xml:space="preserve">39446</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="F83">
+        <is>
+          <t xml:space="preserve">GÖRKEM DOKSÖZ</t>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="G83">
+        <is>
           <t xml:space="preserve">11858</t>
         </is>
       </c>
-      <c s="3" t="inlineStr" r="H17">
+      <c s="3" t="inlineStr" r="H83">
         <is>
           <t xml:space="preserve">PET YDG PRTKL 2.5L 6X LS</t>
         </is>
       </c>
-      <c s="3" t="inlineStr" r="I17">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="3" t="inlineStr" r="J17">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="3" t="inlineStr" r="K17">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="4" r="L17">
-        <v>4</v>
-      </c>
-      <c s="4" r="M17">
-        <v>0</v>
-      </c>
-      <c s="4" r="N17">
-        <v>0</v>
-      </c>
-      <c s="4" r="O17">
-        <v>64.00</v>
-      </c>
-      <c s="4" r="P17">
-        <v>1641.84</v>
-      </c>
-      <c s="4" r="Q17">
-        <v>0</v>
-      </c>
-      <c s="4" r="R17">
-        <v>378.78</v>
-      </c>
-      <c s="4" r="S17">
-        <v>0</v>
-      </c>
-      <c s="4" r="T17">
-        <v>378.78</v>
-      </c>
-      <c s="4" r="U17">
-        <v>1263.06</v>
-      </c>
-      <c s="4" r="V17">
-        <v>126.31</v>
-      </c>
-      <c s="4" r="W17">
-        <v>1389.36</v>
-      </c>
-      <c s="5" t="str" r="X17"/>
-    </row>
-    <row r="18" ht="16.95" customHeight="0">
-      <c s="6" t="inlineStr" r="A18">
+      <c s="3" t="inlineStr" r="I83">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="J83">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="3" t="inlineStr" r="K83">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="4" r="L83">
+        <v>5</v>
+      </c>
+      <c s="4" r="M83">
+        <v>0</v>
+      </c>
+      <c s="4" r="N83">
+        <v>0</v>
+      </c>
+      <c s="4" r="O83">
+        <v>80.00</v>
+      </c>
+      <c s="4" r="P83">
+        <v>2052.30</v>
+      </c>
+      <c s="4" r="Q83">
+        <v>0</v>
+      </c>
+      <c s="4" r="R83">
+        <v>473.48</v>
+      </c>
+      <c s="4" r="S83">
+        <v>0</v>
+      </c>
+      <c s="4" r="T83">
+        <v>473.48</v>
+      </c>
+      <c s="4" r="U83">
+        <v>1578.82</v>
+      </c>
+      <c s="4" r="V83">
+        <v>157.88</v>
+      </c>
+      <c s="4" r="W83">
+        <v>1736.70</v>
+      </c>
+      <c s="5" t="str" r="X83"/>
+    </row>
+    <row r="84" ht="17" customHeight="0">
+      <c s="6" t="inlineStr" r="A84">
         <is>
           <t xml:space="preserve">Toplam</t>
         </is>
       </c>
-      <c s="7" t="str" r="B18"/>
-      <c s="7" t="str" r="C18"/>
-      <c s="7" t="str" r="D18"/>
-      <c s="7" t="str" r="E18"/>
-      <c s="7" t="str" r="F18"/>
-      <c s="7" t="str" r="G18"/>
-      <c s="8" t="str" r="H18"/>
-      <c s="6" t="inlineStr" r="I18">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="6" t="inlineStr" r="J18">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="6" t="inlineStr" r="K18">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="9" r="L18">
-        <v>902</v>
-      </c>
-      <c s="9" r="M18">
-        <v>0</v>
-      </c>
-      <c s="9" r="N18">
-        <v>0</v>
-      </c>
-      <c s="9" r="O18">
-        <v>16778.16</v>
-      </c>
-      <c s="9" r="P18">
-        <v>591720.06</v>
-      </c>
-      <c s="9" r="Q18">
-        <v>21598.13</v>
-      </c>
-      <c s="9" r="R18">
-        <v>127513.34</v>
-      </c>
-      <c s="9" r="S18">
-        <v>0</v>
-      </c>
-      <c s="9" r="T18">
-        <v>149111.47</v>
-      </c>
-      <c s="9" r="U18">
-        <v>442608.59</v>
-      </c>
-      <c s="9" r="V18">
-        <v>44260.86</v>
-      </c>
-      <c s="9" r="W18">
-        <v>486869.45</v>
-      </c>
-      <c s="2" t="str" r="X18"/>
-    </row>
-    <row r="19" ht="0.05" customHeight="1"/>
-    <row r="20" ht="46.5" customHeight="1"/>
+      <c s="7" t="str" r="B84"/>
+      <c s="7" t="str" r="C84"/>
+      <c s="7" t="str" r="D84"/>
+      <c s="7" t="str" r="E84"/>
+      <c s="7" t="str" r="F84"/>
+      <c s="7" t="str" r="G84"/>
+      <c s="8" t="str" r="H84"/>
+      <c s="6" t="inlineStr" r="I84">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="6" t="inlineStr" r="J84">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="6" t="inlineStr" r="K84">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="9" r="L84">
+        <v>3757</v>
+      </c>
+      <c s="9" r="M84">
+        <v>0</v>
+      </c>
+      <c s="9" r="N84">
+        <v>0</v>
+      </c>
+      <c s="9" r="O84">
+        <v>52410.22</v>
+      </c>
+      <c s="9" r="P84">
+        <v>2372084.40</v>
+      </c>
+      <c s="9" r="Q84">
+        <v>1610.88</v>
+      </c>
+      <c s="9" r="R84">
+        <v>745419.68</v>
+      </c>
+      <c s="9" r="S84">
+        <v>0</v>
+      </c>
+      <c s="9" r="T84">
+        <v>747030.56</v>
+      </c>
+      <c s="9" r="U84">
+        <v>1625053.84</v>
+      </c>
+      <c s="9" r="V84">
+        <v>162505.38</v>
+      </c>
+      <c s="9" r="W84">
+        <v>1787559.23</v>
+      </c>
+      <c s="2" t="str" r="X84"/>
+    </row>
+    <row r="85" ht="46.5" customHeight="1"/>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A84:H84"/>
   </mergeCells>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.78740157480315" footer="0.78740157480315"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
